--- a/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>AKO.B</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3002300</v>
+        <v>2775500</v>
       </c>
       <c r="E8" s="3">
-        <v>2504900</v>
+        <v>2816300</v>
       </c>
       <c r="F8" s="3">
-        <v>1919100</v>
+        <v>2349700</v>
       </c>
       <c r="G8" s="3">
-        <v>2010300</v>
+        <v>1800200</v>
       </c>
       <c r="H8" s="3">
-        <v>1890400</v>
+        <v>1885800</v>
       </c>
       <c r="I8" s="3">
-        <v>2089200</v>
+        <v>1773300</v>
       </c>
       <c r="J8" s="3">
+        <v>1959800</v>
+      </c>
+      <c r="K8" s="3">
         <v>2008500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2102700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2138700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1978200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1500500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1484100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1840400</v>
+        <v>1698100</v>
       </c>
       <c r="E9" s="3">
-        <v>1554200</v>
+        <v>1726400</v>
       </c>
       <c r="F9" s="3">
-        <v>1155400</v>
+        <v>1457900</v>
       </c>
       <c r="G9" s="3">
-        <v>1184600</v>
+        <v>1083800</v>
       </c>
       <c r="H9" s="3">
-        <v>1093900</v>
+        <v>1111200</v>
       </c>
       <c r="I9" s="3">
-        <v>1208000</v>
+        <v>1026100</v>
       </c>
       <c r="J9" s="3">
+        <v>1133200</v>
+      </c>
+      <c r="K9" s="3">
         <v>1168300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1239500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1286700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1189300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>894700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>873700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1161800</v>
+        <v>1077400</v>
       </c>
       <c r="E10" s="3">
-        <v>950700</v>
+        <v>1089900</v>
       </c>
       <c r="F10" s="3">
-        <v>763600</v>
+        <v>891800</v>
       </c>
       <c r="G10" s="3">
-        <v>825700</v>
+        <v>716300</v>
       </c>
       <c r="H10" s="3">
-        <v>796500</v>
+        <v>774500</v>
       </c>
       <c r="I10" s="3">
-        <v>881200</v>
+        <v>747200</v>
       </c>
       <c r="J10" s="3">
+        <v>826600</v>
+      </c>
+      <c r="K10" s="3">
         <v>840200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>863200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>852000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>788900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>605900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>610500</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>26100</v>
+        <v>28300</v>
       </c>
       <c r="E14" s="3">
-        <v>500</v>
+        <v>24500</v>
       </c>
       <c r="F14" s="3">
-        <v>9000</v>
+        <v>400</v>
       </c>
       <c r="G14" s="3">
-        <v>3400</v>
+        <v>8500</v>
       </c>
       <c r="H14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
-        <v>3400</v>
-      </c>
       <c r="J14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K14" s="3">
         <v>5400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3700</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2638700</v>
+        <v>2440300</v>
       </c>
       <c r="E17" s="3">
-        <v>2190100</v>
+        <v>2475200</v>
       </c>
       <c r="F17" s="3">
-        <v>1658500</v>
+        <v>2054500</v>
       </c>
       <c r="G17" s="3">
-        <v>1724900</v>
+        <v>1555800</v>
       </c>
       <c r="H17" s="3">
-        <v>1654000</v>
+        <v>1618100</v>
       </c>
       <c r="I17" s="3">
-        <v>1840600</v>
+        <v>1551500</v>
       </c>
       <c r="J17" s="3">
+        <v>1726600</v>
+      </c>
+      <c r="K17" s="3">
         <v>1794600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1892400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1935700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1785800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1320300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1282700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>363600</v>
+        <v>335300</v>
       </c>
       <c r="E18" s="3">
-        <v>314800</v>
+        <v>341100</v>
       </c>
       <c r="F18" s="3">
-        <v>260500</v>
+        <v>295300</v>
       </c>
       <c r="G18" s="3">
-        <v>285400</v>
+        <v>244400</v>
       </c>
       <c r="H18" s="3">
-        <v>236400</v>
+        <v>267700</v>
       </c>
       <c r="I18" s="3">
-        <v>248600</v>
+        <v>221800</v>
       </c>
       <c r="J18" s="3">
+        <v>233200</v>
+      </c>
+      <c r="K18" s="3">
         <v>213900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>210300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>202900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>192400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>180200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>201500</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-37500</v>
+        <v>4800</v>
       </c>
       <c r="E20" s="3">
-        <v>-27900</v>
+        <v>-35200</v>
       </c>
       <c r="F20" s="3">
-        <v>-6100</v>
+        <v>-26100</v>
       </c>
       <c r="G20" s="3">
-        <v>26400</v>
+        <v>-5700</v>
       </c>
       <c r="H20" s="3">
-        <v>-17900</v>
+        <v>24800</v>
       </c>
       <c r="I20" s="3">
-        <v>-1700</v>
+        <v>-16800</v>
       </c>
       <c r="J20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8300</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>326100</v>
+        <v>340000</v>
       </c>
       <c r="E21" s="3">
-        <v>286900</v>
+        <v>305900</v>
       </c>
       <c r="F21" s="3">
-        <v>254400</v>
+        <v>269200</v>
       </c>
       <c r="G21" s="3">
-        <v>311800</v>
+        <v>238600</v>
       </c>
       <c r="H21" s="3">
-        <v>218500</v>
+        <v>292500</v>
       </c>
       <c r="I21" s="3">
-        <v>246900</v>
+        <v>205000</v>
       </c>
       <c r="J21" s="3">
+        <v>231600</v>
+      </c>
+      <c r="K21" s="3">
         <v>210700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>201500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>187800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>181900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>246000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>268700</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>63000</v>
+        <v>63900</v>
       </c>
       <c r="E22" s="3">
-        <v>57300</v>
+        <v>59100</v>
       </c>
       <c r="F22" s="3">
-        <v>53200</v>
+        <v>53800</v>
       </c>
       <c r="G22" s="3">
-        <v>44600</v>
+        <v>49900</v>
       </c>
       <c r="H22" s="3">
-        <v>45600</v>
+        <v>41900</v>
       </c>
       <c r="I22" s="3">
-        <v>53900</v>
+        <v>42800</v>
       </c>
       <c r="J22" s="3">
+        <v>50600</v>
+      </c>
+      <c r="K22" s="3">
         <v>51600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>56200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>71300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>34700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>10900</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>263100</v>
+        <v>276100</v>
       </c>
       <c r="E23" s="3">
-        <v>229600</v>
+        <v>246800</v>
       </c>
       <c r="F23" s="3">
-        <v>201200</v>
+        <v>215400</v>
       </c>
       <c r="G23" s="3">
-        <v>267100</v>
+        <v>188700</v>
       </c>
       <c r="H23" s="3">
-        <v>172900</v>
+        <v>250600</v>
       </c>
       <c r="I23" s="3">
-        <v>193000</v>
+        <v>162200</v>
       </c>
       <c r="J23" s="3">
+        <v>181000</v>
+      </c>
+      <c r="K23" s="3">
         <v>159200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>145300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>116400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>147200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>162300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>198900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>117900</v>
+        <v>91200</v>
       </c>
       <c r="E24" s="3">
-        <v>52200</v>
+        <v>110600</v>
       </c>
       <c r="F24" s="3">
-        <v>62000</v>
+        <v>48900</v>
       </c>
       <c r="G24" s="3">
-        <v>69100</v>
+        <v>58200</v>
       </c>
       <c r="H24" s="3">
-        <v>62800</v>
+        <v>64800</v>
       </c>
       <c r="I24" s="3">
-        <v>58500</v>
+        <v>58900</v>
       </c>
       <c r="J24" s="3">
+        <v>54900</v>
+      </c>
+      <c r="K24" s="3">
         <v>55200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>46600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>49300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>52400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>145200</v>
+        <v>185000</v>
       </c>
       <c r="E26" s="3">
-        <v>177400</v>
+        <v>136200</v>
       </c>
       <c r="F26" s="3">
-        <v>139100</v>
+        <v>166500</v>
       </c>
       <c r="G26" s="3">
-        <v>198000</v>
+        <v>130500</v>
       </c>
       <c r="H26" s="3">
-        <v>110100</v>
+        <v>185800</v>
       </c>
       <c r="I26" s="3">
-        <v>134500</v>
+        <v>103300</v>
       </c>
       <c r="J26" s="3">
+        <v>126100</v>
+      </c>
+      <c r="K26" s="3">
         <v>104000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>98700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>90200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>117300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>113000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>146500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>141800</v>
+        <v>181700</v>
       </c>
       <c r="E27" s="3">
-        <v>174800</v>
+        <v>133000</v>
       </c>
       <c r="F27" s="3">
-        <v>137900</v>
+        <v>164000</v>
       </c>
       <c r="G27" s="3">
-        <v>196300</v>
+        <v>129300</v>
       </c>
       <c r="H27" s="3">
-        <v>109200</v>
+        <v>184100</v>
       </c>
       <c r="I27" s="3">
-        <v>133200</v>
+        <v>102400</v>
       </c>
       <c r="J27" s="3">
+        <v>124900</v>
+      </c>
+      <c r="K27" s="3">
         <v>102300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>98400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>89800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>115700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>112200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>146500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>37500</v>
+        <v>-4800</v>
       </c>
       <c r="E32" s="3">
-        <v>27900</v>
+        <v>35200</v>
       </c>
       <c r="F32" s="3">
-        <v>6100</v>
+        <v>26100</v>
       </c>
       <c r="G32" s="3">
-        <v>-26400</v>
+        <v>5700</v>
       </c>
       <c r="H32" s="3">
-        <v>17900</v>
+        <v>-24800</v>
       </c>
       <c r="I32" s="3">
-        <v>1700</v>
+        <v>16800</v>
       </c>
       <c r="J32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K32" s="3">
         <v>3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8300</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>141800</v>
+        <v>181700</v>
       </c>
       <c r="E33" s="3">
-        <v>174800</v>
+        <v>133000</v>
       </c>
       <c r="F33" s="3">
-        <v>137900</v>
+        <v>164000</v>
       </c>
       <c r="G33" s="3">
-        <v>196300</v>
+        <v>129300</v>
       </c>
       <c r="H33" s="3">
-        <v>109200</v>
+        <v>184100</v>
       </c>
       <c r="I33" s="3">
-        <v>133200</v>
+        <v>102400</v>
       </c>
       <c r="J33" s="3">
+        <v>124900</v>
+      </c>
+      <c r="K33" s="3">
         <v>102300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>98400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>89800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>115700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>112200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>146500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>141800</v>
+        <v>181700</v>
       </c>
       <c r="E35" s="3">
-        <v>174800</v>
+        <v>133000</v>
       </c>
       <c r="F35" s="3">
-        <v>137900</v>
+        <v>164000</v>
       </c>
       <c r="G35" s="3">
-        <v>196300</v>
+        <v>129300</v>
       </c>
       <c r="H35" s="3">
-        <v>109200</v>
+        <v>184100</v>
       </c>
       <c r="I35" s="3">
-        <v>133200</v>
+        <v>102400</v>
       </c>
       <c r="J35" s="3">
+        <v>124900</v>
+      </c>
+      <c r="K35" s="3">
         <v>102300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>98400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>89800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>115700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>112200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>146500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>122800</v>
+        <v>127100</v>
       </c>
       <c r="E41" s="3">
-        <v>107300</v>
+        <v>115200</v>
       </c>
       <c r="F41" s="3">
-        <v>94200</v>
+        <v>100700</v>
       </c>
       <c r="G41" s="3">
-        <v>60500</v>
+        <v>88300</v>
       </c>
       <c r="H41" s="3">
-        <v>57400</v>
+        <v>56700</v>
       </c>
       <c r="I41" s="3">
-        <v>45200</v>
+        <v>53900</v>
       </c>
       <c r="J41" s="3">
+        <v>42400</v>
+      </c>
+      <c r="K41" s="3">
         <v>31500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>45300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>94600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>104000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>32100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24900</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>311700</v>
+        <v>265000</v>
       </c>
       <c r="E42" s="3">
-        <v>456300</v>
+        <v>292400</v>
       </c>
       <c r="F42" s="3">
-        <v>414100</v>
+        <v>428100</v>
       </c>
       <c r="G42" s="3">
-        <v>117600</v>
+        <v>388500</v>
       </c>
       <c r="H42" s="3">
-        <v>98000</v>
+        <v>110300</v>
       </c>
       <c r="I42" s="3">
-        <v>124200</v>
+        <v>91900</v>
       </c>
       <c r="J42" s="3">
+        <v>116500</v>
+      </c>
+      <c r="K42" s="3">
         <v>190800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>197300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>126800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>47400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>39000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22400</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>378600</v>
+        <v>380900</v>
       </c>
       <c r="E43" s="3">
-        <v>324500</v>
+        <v>355200</v>
       </c>
       <c r="F43" s="3">
-        <v>233200</v>
+        <v>304400</v>
       </c>
       <c r="G43" s="3">
-        <v>239500</v>
+        <v>218700</v>
       </c>
       <c r="H43" s="3">
-        <v>200500</v>
+        <v>224600</v>
       </c>
       <c r="I43" s="3">
-        <v>213300</v>
+        <v>188100</v>
       </c>
       <c r="J43" s="3">
+        <v>200100</v>
+      </c>
+      <c r="K43" s="3">
         <v>213800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>204300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>244600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>269000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>202400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>228100</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>277900</v>
+        <v>247000</v>
       </c>
       <c r="E44" s="3">
-        <v>216200</v>
+        <v>260600</v>
       </c>
       <c r="F44" s="3">
-        <v>144600</v>
+        <v>202800</v>
       </c>
       <c r="G44" s="3">
-        <v>166800</v>
+        <v>135700</v>
       </c>
       <c r="H44" s="3">
-        <v>171000</v>
+        <v>156500</v>
       </c>
       <c r="I44" s="3">
-        <v>148400</v>
+        <v>160400</v>
       </c>
       <c r="J44" s="3">
+        <v>139200</v>
+      </c>
+      <c r="K44" s="3">
         <v>163500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>149300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>178200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>163600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>114300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>86800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>221800</v>
+        <v>20600</v>
       </c>
       <c r="E45" s="3">
-        <v>15400</v>
+        <v>208000</v>
       </c>
       <c r="F45" s="3">
-        <v>14800</v>
+        <v>14500</v>
       </c>
       <c r="G45" s="3">
-        <v>18400</v>
+        <v>13900</v>
       </c>
       <c r="H45" s="3">
         <v>17300</v>
       </c>
       <c r="I45" s="3">
-        <v>15800</v>
+        <v>16200</v>
       </c>
       <c r="J45" s="3">
+        <v>14800</v>
+      </c>
+      <c r="K45" s="3">
         <v>24900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>49700</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1312800</v>
+        <v>1040700</v>
       </c>
       <c r="E46" s="3">
-        <v>1119800</v>
+        <v>1231400</v>
       </c>
       <c r="F46" s="3">
-        <v>900900</v>
+        <v>1050400</v>
       </c>
       <c r="G46" s="3">
-        <v>602800</v>
+        <v>845100</v>
       </c>
       <c r="H46" s="3">
-        <v>544200</v>
+        <v>565500</v>
       </c>
       <c r="I46" s="3">
-        <v>546900</v>
+        <v>510500</v>
       </c>
       <c r="J46" s="3">
+        <v>513100</v>
+      </c>
+      <c r="K46" s="3">
         <v>624600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>613100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>658900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>598800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>418800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>355700</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>173400</v>
+        <v>154700</v>
       </c>
       <c r="E47" s="3">
-        <v>164600</v>
+        <v>162700</v>
       </c>
       <c r="F47" s="3">
-        <v>187200</v>
+        <v>154400</v>
       </c>
       <c r="G47" s="3">
-        <v>232100</v>
+        <v>175600</v>
       </c>
       <c r="H47" s="3">
-        <v>132300</v>
+        <v>217800</v>
       </c>
       <c r="I47" s="3">
-        <v>103600</v>
+        <v>124100</v>
       </c>
       <c r="J47" s="3">
+        <v>97100</v>
+      </c>
+      <c r="K47" s="3">
         <v>94700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>70800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>147800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>109500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>102200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>101900</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>902000</v>
+        <v>924700</v>
       </c>
       <c r="E48" s="3">
-        <v>809500</v>
+        <v>846100</v>
       </c>
       <c r="F48" s="3">
-        <v>684300</v>
+        <v>759400</v>
       </c>
       <c r="G48" s="3">
-        <v>816700</v>
+        <v>641900</v>
       </c>
       <c r="H48" s="3">
-        <v>803200</v>
+        <v>766100</v>
       </c>
       <c r="I48" s="3">
-        <v>745500</v>
+        <v>753400</v>
       </c>
       <c r="J48" s="3">
+        <v>699300</v>
+      </c>
+      <c r="K48" s="3">
         <v>752800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>717400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>848600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>900800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>738000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>528600</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>904900</v>
+        <v>867100</v>
       </c>
       <c r="E49" s="3">
-        <v>878800</v>
+        <v>848900</v>
       </c>
       <c r="F49" s="3">
-        <v>794200</v>
+        <v>824300</v>
       </c>
       <c r="G49" s="3">
-        <v>899800</v>
+        <v>745000</v>
       </c>
       <c r="H49" s="3">
-        <v>888200</v>
+        <v>844100</v>
       </c>
       <c r="I49" s="3">
-        <v>855300</v>
+        <v>833200</v>
       </c>
       <c r="J49" s="3">
+        <v>802300</v>
+      </c>
+      <c r="K49" s="3">
         <v>885800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>852900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1005700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1061300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>677600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>88600</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>109000</v>
+        <v>109600</v>
       </c>
       <c r="E52" s="3">
-        <v>356400</v>
+        <v>102300</v>
       </c>
       <c r="F52" s="3">
-        <v>199700</v>
+        <v>334300</v>
       </c>
       <c r="G52" s="3">
-        <v>150300</v>
+        <v>187300</v>
       </c>
       <c r="H52" s="3">
-        <v>134500</v>
+        <v>141000</v>
       </c>
       <c r="I52" s="3">
-        <v>138500</v>
+        <v>126200</v>
       </c>
       <c r="J52" s="3">
+        <v>129900</v>
+      </c>
+      <c r="K52" s="3">
         <v>127100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>220300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>39300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>37400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>34500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>45600</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3402100</v>
+        <v>3096800</v>
       </c>
       <c r="E54" s="3">
-        <v>3329100</v>
+        <v>3191300</v>
       </c>
       <c r="F54" s="3">
-        <v>2766300</v>
+        <v>3122900</v>
       </c>
       <c r="G54" s="3">
-        <v>2701800</v>
+        <v>2594900</v>
       </c>
       <c r="H54" s="3">
-        <v>2502400</v>
+        <v>2534400</v>
       </c>
       <c r="I54" s="3">
-        <v>2389800</v>
+        <v>2347400</v>
       </c>
       <c r="J54" s="3">
+        <v>2241800</v>
+      </c>
+      <c r="K54" s="3">
         <v>2485000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2474500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2700300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2707800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1971000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1120400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>536800</v>
+        <v>556500</v>
       </c>
       <c r="E57" s="3">
-        <v>433400</v>
+        <v>503600</v>
       </c>
       <c r="F57" s="3">
-        <v>305100</v>
+        <v>406500</v>
       </c>
       <c r="G57" s="3">
-        <v>336000</v>
+        <v>286200</v>
       </c>
       <c r="H57" s="3">
-        <v>320800</v>
+        <v>315200</v>
       </c>
       <c r="I57" s="3">
-        <v>329400</v>
+        <v>301000</v>
       </c>
       <c r="J57" s="3">
+        <v>309000</v>
+      </c>
+      <c r="K57" s="3">
         <v>324300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>292500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>257900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>268300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>245700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>187700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>393900</v>
+        <v>41200</v>
       </c>
       <c r="E58" s="3">
-        <v>38000</v>
+        <v>369500</v>
       </c>
       <c r="F58" s="3">
-        <v>28500</v>
+        <v>35600</v>
       </c>
       <c r="G58" s="3">
-        <v>32800</v>
+        <v>26700</v>
       </c>
       <c r="H58" s="3">
-        <v>49400</v>
+        <v>30800</v>
       </c>
       <c r="I58" s="3">
-        <v>60700</v>
+        <v>46400</v>
       </c>
       <c r="J58" s="3">
+        <v>56900</v>
+      </c>
+      <c r="K58" s="3">
         <v>56600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>51400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>94000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>137600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>136000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>34900</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>142000</v>
+        <v>136700</v>
       </c>
       <c r="E59" s="3">
-        <v>127100</v>
+        <v>133200</v>
       </c>
       <c r="F59" s="3">
-        <v>93600</v>
+        <v>119200</v>
       </c>
       <c r="G59" s="3">
-        <v>96300</v>
+        <v>87800</v>
       </c>
       <c r="H59" s="3">
-        <v>104200</v>
+        <v>90400</v>
       </c>
       <c r="I59" s="3">
-        <v>93900</v>
+        <v>97700</v>
       </c>
       <c r="J59" s="3">
+        <v>88100</v>
+      </c>
+      <c r="K59" s="3">
         <v>93200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>82400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>136200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>116900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>60400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>74300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1072600</v>
+        <v>734400</v>
       </c>
       <c r="E60" s="3">
-        <v>598400</v>
+        <v>1006200</v>
       </c>
       <c r="F60" s="3">
-        <v>427200</v>
+        <v>561300</v>
       </c>
       <c r="G60" s="3">
-        <v>465200</v>
+        <v>400700</v>
       </c>
       <c r="H60" s="3">
-        <v>474400</v>
+        <v>436400</v>
       </c>
       <c r="I60" s="3">
-        <v>484000</v>
+        <v>445100</v>
       </c>
       <c r="J60" s="3">
+        <v>454000</v>
+      </c>
+      <c r="K60" s="3">
         <v>474100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>426200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>488200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>522800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>442100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>296900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>895700</v>
+        <v>1051400</v>
       </c>
       <c r="E61" s="3">
-        <v>1176400</v>
+        <v>840200</v>
       </c>
       <c r="F61" s="3">
-        <v>1060200</v>
+        <v>1103500</v>
       </c>
       <c r="G61" s="3">
-        <v>840000</v>
+        <v>994600</v>
       </c>
       <c r="H61" s="3">
-        <v>809700</v>
+        <v>787900</v>
       </c>
       <c r="I61" s="3">
-        <v>763600</v>
+        <v>759600</v>
       </c>
       <c r="J61" s="3">
+        <v>716300</v>
+      </c>
+      <c r="K61" s="3">
         <v>815400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>857100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>864700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>785700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>222600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>112700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>435500</v>
+        <v>334700</v>
       </c>
       <c r="E62" s="3">
-        <v>309700</v>
+        <v>408600</v>
       </c>
       <c r="F62" s="3">
-        <v>339200</v>
+        <v>290500</v>
       </c>
       <c r="G62" s="3">
-        <v>301800</v>
+        <v>318200</v>
       </c>
       <c r="H62" s="3">
-        <v>242200</v>
+        <v>283100</v>
       </c>
       <c r="I62" s="3">
-        <v>223300</v>
+        <v>227200</v>
       </c>
       <c r="J62" s="3">
+        <v>209400</v>
+      </c>
+      <c r="K62" s="3">
         <v>243900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>237400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>253900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>253500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>162500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>73500</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2435600</v>
+        <v>2157300</v>
       </c>
       <c r="E66" s="3">
-        <v>2113100</v>
+        <v>2284800</v>
       </c>
       <c r="F66" s="3">
-        <v>1849700</v>
+        <v>1982200</v>
       </c>
       <c r="G66" s="3">
-        <v>1629800</v>
+        <v>1735100</v>
       </c>
       <c r="H66" s="3">
-        <v>1548900</v>
+        <v>1528800</v>
       </c>
       <c r="I66" s="3">
-        <v>1495600</v>
+        <v>1452900</v>
       </c>
       <c r="J66" s="3">
+        <v>1403000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1557700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1544400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1632500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1589000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>852100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>483200</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1299600</v>
+        <v>1274600</v>
       </c>
       <c r="E72" s="3">
-        <v>1357400</v>
+        <v>1219100</v>
       </c>
       <c r="F72" s="3">
-        <v>1228700</v>
+        <v>1273300</v>
       </c>
       <c r="G72" s="3">
-        <v>1168500</v>
+        <v>1152600</v>
       </c>
       <c r="H72" s="3">
-        <v>1011800</v>
+        <v>1096100</v>
       </c>
       <c r="I72" s="3">
-        <v>861800</v>
+        <v>949100</v>
       </c>
       <c r="J72" s="3">
+        <v>808400</v>
+      </c>
+      <c r="K72" s="3">
         <v>816800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>786100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>803200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>871400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>853700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>322400</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>966400</v>
+        <v>939500</v>
       </c>
       <c r="E76" s="3">
-        <v>1216000</v>
+        <v>906600</v>
       </c>
       <c r="F76" s="3">
-        <v>916600</v>
+        <v>1140700</v>
       </c>
       <c r="G76" s="3">
-        <v>1072000</v>
+        <v>859900</v>
       </c>
       <c r="H76" s="3">
-        <v>953500</v>
+        <v>1005600</v>
       </c>
       <c r="I76" s="3">
-        <v>894200</v>
+        <v>894400</v>
       </c>
       <c r="J76" s="3">
+        <v>838800</v>
+      </c>
+      <c r="K76" s="3">
         <v>927300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>930100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1067800</v>
-      </c>
-      <c r="M76" s="3">
-        <v>1118900</v>
       </c>
       <c r="N76" s="3">
         <v>1118900</v>
       </c>
       <c r="O76" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="P76" s="3">
         <v>637200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>141800</v>
+        <v>181700</v>
       </c>
       <c r="E81" s="3">
-        <v>174800</v>
+        <v>133000</v>
       </c>
       <c r="F81" s="3">
-        <v>137900</v>
+        <v>164000</v>
       </c>
       <c r="G81" s="3">
-        <v>196300</v>
+        <v>129300</v>
       </c>
       <c r="H81" s="3">
-        <v>109200</v>
+        <v>184100</v>
       </c>
       <c r="I81" s="3">
-        <v>133200</v>
+        <v>102400</v>
       </c>
       <c r="J81" s="3">
+        <v>124900</v>
+      </c>
+      <c r="K81" s="3">
         <v>102300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>98400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>89800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>115700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>112200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>146500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,8 +3687,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3526,14 +3724,17 @@
         <v>0</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>68900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>59700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>430400</v>
+        <v>374000</v>
       </c>
       <c r="E89" s="3">
-        <v>337700</v>
+        <v>403700</v>
       </c>
       <c r="F89" s="3">
-        <v>312300</v>
+        <v>316800</v>
       </c>
       <c r="G89" s="3">
-        <v>286100</v>
+        <v>293000</v>
       </c>
       <c r="H89" s="3">
-        <v>260400</v>
+        <v>268300</v>
       </c>
       <c r="I89" s="3">
-        <v>280200</v>
+        <v>244300</v>
       </c>
       <c r="J89" s="3">
+        <v>262800</v>
+      </c>
+      <c r="K89" s="3">
         <v>252500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>296700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>256500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>223700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>241700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>209800</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-211000</v>
+        <v>-204300</v>
       </c>
       <c r="E91" s="3">
-        <v>-156900</v>
+        <v>-197900</v>
       </c>
       <c r="F91" s="3">
-        <v>-97000</v>
+        <v>-147200</v>
       </c>
       <c r="G91" s="3">
-        <v>-125100</v>
+        <v>-91000</v>
       </c>
       <c r="H91" s="3">
-        <v>-136800</v>
+        <v>-117300</v>
       </c>
       <c r="I91" s="3">
-        <v>-190800</v>
+        <v>-128300</v>
       </c>
       <c r="J91" s="3">
+        <v>-179000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-144900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-125900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-135900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-238800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-184000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-191700</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-96200</v>
+        <v>-167800</v>
       </c>
       <c r="E94" s="3">
-        <v>-224000</v>
+        <v>-90300</v>
       </c>
       <c r="F94" s="3">
-        <v>-253000</v>
+        <v>-210100</v>
       </c>
       <c r="G94" s="3">
-        <v>-124400</v>
+        <v>-237300</v>
       </c>
       <c r="H94" s="3">
-        <v>-133400</v>
+        <v>-116700</v>
       </c>
       <c r="I94" s="3">
-        <v>-190800</v>
+        <v>-125200</v>
       </c>
       <c r="J94" s="3">
+        <v>-179000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-128700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-115500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-198500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-581800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-199900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-135300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-310000</v>
+        <v>-175800</v>
       </c>
       <c r="E96" s="3">
-        <v>-120200</v>
+        <v>-290800</v>
       </c>
       <c r="F96" s="3">
-        <v>-113000</v>
+        <v>-112700</v>
       </c>
       <c r="G96" s="3">
-        <v>-97500</v>
+        <v>-106000</v>
       </c>
       <c r="H96" s="3">
-        <v>-98900</v>
+        <v>-91400</v>
       </c>
       <c r="I96" s="3">
-        <v>-84700</v>
+        <v>-92800</v>
       </c>
       <c r="J96" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-76400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-60800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-62200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-95000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-89300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-107100</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-324300</v>
+        <v>-198400</v>
       </c>
       <c r="E100" s="3">
-        <v>-130300</v>
+        <v>-304200</v>
       </c>
       <c r="F100" s="3">
-        <v>127700</v>
+        <v>-122200</v>
       </c>
       <c r="G100" s="3">
-        <v>-143600</v>
+        <v>119800</v>
       </c>
       <c r="H100" s="3">
-        <v>-129500</v>
+        <v>-134700</v>
       </c>
       <c r="I100" s="3">
-        <v>-88500</v>
+        <v>-121500</v>
       </c>
       <c r="J100" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-111000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-110400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-55800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>394000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-101400</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-24100</v>
+        <v>4800</v>
       </c>
       <c r="E101" s="3">
-        <v>10700</v>
+        <v>-22600</v>
       </c>
       <c r="F101" s="3">
-        <v>-15300</v>
+        <v>10100</v>
       </c>
       <c r="G101" s="3">
-        <v>4600</v>
+        <v>-14400</v>
       </c>
       <c r="H101" s="3">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="I101" s="3">
-        <v>-6600</v>
+        <v>3800</v>
       </c>
       <c r="J101" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-15200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1300</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-14300</v>
+        <v>12700</v>
       </c>
       <c r="E102" s="3">
-        <v>-5900</v>
+        <v>-13400</v>
       </c>
       <c r="F102" s="3">
-        <v>171700</v>
+        <v>-5500</v>
       </c>
       <c r="G102" s="3">
-        <v>22600</v>
+        <v>161100</v>
       </c>
       <c r="H102" s="3">
-        <v>1500</v>
+        <v>21200</v>
       </c>
       <c r="I102" s="3">
-        <v>-5700</v>
+        <v>1400</v>
       </c>
       <c r="J102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="K102" s="3">
         <v>13700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>31800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>31000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-25600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2775500</v>
+        <v>2854100</v>
       </c>
       <c r="E8" s="3">
-        <v>2816300</v>
+        <v>2896000</v>
       </c>
       <c r="F8" s="3">
-        <v>2349700</v>
+        <v>2416200</v>
       </c>
       <c r="G8" s="3">
-        <v>1800200</v>
+        <v>1851100</v>
       </c>
       <c r="H8" s="3">
-        <v>1885800</v>
+        <v>1939100</v>
       </c>
       <c r="I8" s="3">
-        <v>1773300</v>
+        <v>1823500</v>
       </c>
       <c r="J8" s="3">
-        <v>1959800</v>
+        <v>2015300</v>
       </c>
       <c r="K8" s="3">
         <v>2008500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1698100</v>
+        <v>1746200</v>
       </c>
       <c r="E9" s="3">
-        <v>1726400</v>
+        <v>1775300</v>
       </c>
       <c r="F9" s="3">
-        <v>1457900</v>
+        <v>1499200</v>
       </c>
       <c r="G9" s="3">
-        <v>1083800</v>
+        <v>1114500</v>
       </c>
       <c r="H9" s="3">
-        <v>1111200</v>
+        <v>1142700</v>
       </c>
       <c r="I9" s="3">
-        <v>1026100</v>
+        <v>1055200</v>
       </c>
       <c r="J9" s="3">
-        <v>1133200</v>
+        <v>1165200</v>
       </c>
       <c r="K9" s="3">
         <v>1168300</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1077400</v>
+        <v>1107900</v>
       </c>
       <c r="E10" s="3">
-        <v>1089900</v>
+        <v>1120700</v>
       </c>
       <c r="F10" s="3">
-        <v>891800</v>
+        <v>917100</v>
       </c>
       <c r="G10" s="3">
-        <v>716300</v>
+        <v>736600</v>
       </c>
       <c r="H10" s="3">
-        <v>774500</v>
+        <v>796400</v>
       </c>
       <c r="I10" s="3">
-        <v>747200</v>
+        <v>768300</v>
       </c>
       <c r="J10" s="3">
-        <v>826600</v>
+        <v>850000</v>
       </c>
       <c r="K10" s="3">
         <v>840200</v>
@@ -970,16 +970,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>28300</v>
+        <v>29100</v>
       </c>
       <c r="E14" s="3">
-        <v>24500</v>
+        <v>25200</v>
       </c>
       <c r="F14" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G14" s="3">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="H14" s="3">
         <v>3200</v>
@@ -988,7 +988,7 @@
         <v>300</v>
       </c>
       <c r="J14" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="K14" s="3">
         <v>5400</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2440300</v>
+        <v>2509300</v>
       </c>
       <c r="E17" s="3">
-        <v>2475200</v>
+        <v>2545300</v>
       </c>
       <c r="F17" s="3">
-        <v>2054500</v>
+        <v>2112600</v>
       </c>
       <c r="G17" s="3">
-        <v>1555800</v>
+        <v>1599800</v>
       </c>
       <c r="H17" s="3">
-        <v>1618100</v>
+        <v>1663900</v>
       </c>
       <c r="I17" s="3">
-        <v>1551500</v>
+        <v>1595400</v>
       </c>
       <c r="J17" s="3">
-        <v>1726600</v>
+        <v>1775400</v>
       </c>
       <c r="K17" s="3">
         <v>1794600</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>335300</v>
+        <v>344800</v>
       </c>
       <c r="E18" s="3">
-        <v>341100</v>
+        <v>350700</v>
       </c>
       <c r="F18" s="3">
-        <v>295300</v>
+        <v>303600</v>
       </c>
       <c r="G18" s="3">
-        <v>244400</v>
+        <v>251300</v>
       </c>
       <c r="H18" s="3">
-        <v>267700</v>
+        <v>275300</v>
       </c>
       <c r="I18" s="3">
-        <v>221800</v>
+        <v>228000</v>
       </c>
       <c r="J18" s="3">
-        <v>233200</v>
+        <v>239800</v>
       </c>
       <c r="K18" s="3">
         <v>213900</v>
@@ -1185,22 +1185,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="E20" s="3">
-        <v>-35200</v>
+        <v>-36200</v>
       </c>
       <c r="F20" s="3">
-        <v>-26100</v>
+        <v>-26900</v>
       </c>
       <c r="G20" s="3">
-        <v>-5700</v>
+        <v>-5900</v>
       </c>
       <c r="H20" s="3">
-        <v>24800</v>
+        <v>25500</v>
       </c>
       <c r="I20" s="3">
-        <v>-16800</v>
+        <v>-17200</v>
       </c>
       <c r="J20" s="3">
         <v>-1600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>340000</v>
+        <v>349700</v>
       </c>
       <c r="E21" s="3">
-        <v>305900</v>
+        <v>314500</v>
       </c>
       <c r="F21" s="3">
-        <v>269200</v>
+        <v>276800</v>
       </c>
       <c r="G21" s="3">
-        <v>238600</v>
+        <v>245400</v>
       </c>
       <c r="H21" s="3">
-        <v>292500</v>
+        <v>300700</v>
       </c>
       <c r="I21" s="3">
-        <v>205000</v>
+        <v>210800</v>
       </c>
       <c r="J21" s="3">
-        <v>231600</v>
+        <v>238200</v>
       </c>
       <c r="K21" s="3">
         <v>210700</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>63900</v>
+        <v>65700</v>
       </c>
       <c r="E22" s="3">
-        <v>59100</v>
+        <v>60800</v>
       </c>
       <c r="F22" s="3">
-        <v>53800</v>
+        <v>55300</v>
       </c>
       <c r="G22" s="3">
-        <v>49900</v>
+        <v>51400</v>
       </c>
       <c r="H22" s="3">
-        <v>41900</v>
+        <v>43000</v>
       </c>
       <c r="I22" s="3">
-        <v>42800</v>
+        <v>44000</v>
       </c>
       <c r="J22" s="3">
-        <v>50600</v>
+        <v>52000</v>
       </c>
       <c r="K22" s="3">
         <v>51600</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>276100</v>
+        <v>284000</v>
       </c>
       <c r="E23" s="3">
-        <v>246800</v>
+        <v>253800</v>
       </c>
       <c r="F23" s="3">
-        <v>215400</v>
+        <v>221500</v>
       </c>
       <c r="G23" s="3">
-        <v>188700</v>
+        <v>194000</v>
       </c>
       <c r="H23" s="3">
-        <v>250600</v>
+        <v>257700</v>
       </c>
       <c r="I23" s="3">
-        <v>162200</v>
+        <v>166800</v>
       </c>
       <c r="J23" s="3">
-        <v>181000</v>
+        <v>186200</v>
       </c>
       <c r="K23" s="3">
         <v>159200</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>91200</v>
+        <v>93700</v>
       </c>
       <c r="E24" s="3">
-        <v>110600</v>
+        <v>113700</v>
       </c>
       <c r="F24" s="3">
-        <v>48900</v>
+        <v>50300</v>
       </c>
       <c r="G24" s="3">
-        <v>58200</v>
+        <v>59800</v>
       </c>
       <c r="H24" s="3">
-        <v>64800</v>
+        <v>66700</v>
       </c>
       <c r="I24" s="3">
-        <v>58900</v>
+        <v>60600</v>
       </c>
       <c r="J24" s="3">
-        <v>54900</v>
+        <v>56500</v>
       </c>
       <c r="K24" s="3">
         <v>55200</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>185000</v>
+        <v>190200</v>
       </c>
       <c r="E26" s="3">
-        <v>136200</v>
+        <v>140000</v>
       </c>
       <c r="F26" s="3">
-        <v>166500</v>
+        <v>171200</v>
       </c>
       <c r="G26" s="3">
-        <v>130500</v>
+        <v>134200</v>
       </c>
       <c r="H26" s="3">
-        <v>185800</v>
+        <v>191000</v>
       </c>
       <c r="I26" s="3">
-        <v>103300</v>
+        <v>106200</v>
       </c>
       <c r="J26" s="3">
-        <v>126100</v>
+        <v>129700</v>
       </c>
       <c r="K26" s="3">
         <v>104000</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>181700</v>
+        <v>186900</v>
       </c>
       <c r="E27" s="3">
+        <v>136800</v>
+      </c>
+      <c r="F27" s="3">
+        <v>168600</v>
+      </c>
+      <c r="G27" s="3">
         <v>133000</v>
       </c>
-      <c r="F27" s="3">
-        <v>164000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>129300</v>
-      </c>
       <c r="H27" s="3">
-        <v>184100</v>
+        <v>189400</v>
       </c>
       <c r="I27" s="3">
-        <v>102400</v>
+        <v>105300</v>
       </c>
       <c r="J27" s="3">
-        <v>124900</v>
+        <v>128400</v>
       </c>
       <c r="K27" s="3">
         <v>102300</v>
@@ -1725,22 +1725,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4800</v>
+        <v>-4900</v>
       </c>
       <c r="E32" s="3">
-        <v>35200</v>
+        <v>36200</v>
       </c>
       <c r="F32" s="3">
-        <v>26100</v>
+        <v>26900</v>
       </c>
       <c r="G32" s="3">
-        <v>5700</v>
+        <v>5900</v>
       </c>
       <c r="H32" s="3">
-        <v>-24800</v>
+        <v>-25500</v>
       </c>
       <c r="I32" s="3">
-        <v>16800</v>
+        <v>17200</v>
       </c>
       <c r="J32" s="3">
         <v>1600</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>181700</v>
+        <v>186900</v>
       </c>
       <c r="E33" s="3">
+        <v>136800</v>
+      </c>
+      <c r="F33" s="3">
+        <v>168600</v>
+      </c>
+      <c r="G33" s="3">
         <v>133000</v>
       </c>
-      <c r="F33" s="3">
-        <v>164000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>129300</v>
-      </c>
       <c r="H33" s="3">
-        <v>184100</v>
+        <v>189400</v>
       </c>
       <c r="I33" s="3">
-        <v>102400</v>
+        <v>105300</v>
       </c>
       <c r="J33" s="3">
-        <v>124900</v>
+        <v>128400</v>
       </c>
       <c r="K33" s="3">
         <v>102300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>181700</v>
+        <v>186900</v>
       </c>
       <c r="E35" s="3">
+        <v>136800</v>
+      </c>
+      <c r="F35" s="3">
+        <v>168600</v>
+      </c>
+      <c r="G35" s="3">
         <v>133000</v>
       </c>
-      <c r="F35" s="3">
-        <v>164000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>129300</v>
-      </c>
       <c r="H35" s="3">
-        <v>184100</v>
+        <v>189400</v>
       </c>
       <c r="I35" s="3">
-        <v>102400</v>
+        <v>105300</v>
       </c>
       <c r="J35" s="3">
-        <v>124900</v>
+        <v>128400</v>
       </c>
       <c r="K35" s="3">
         <v>102300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>127100</v>
+        <v>130700</v>
       </c>
       <c r="E41" s="3">
-        <v>115200</v>
+        <v>118500</v>
       </c>
       <c r="F41" s="3">
-        <v>100700</v>
+        <v>103500</v>
       </c>
       <c r="G41" s="3">
-        <v>88300</v>
+        <v>90800</v>
       </c>
       <c r="H41" s="3">
-        <v>56700</v>
+        <v>58300</v>
       </c>
       <c r="I41" s="3">
-        <v>53900</v>
+        <v>55400</v>
       </c>
       <c r="J41" s="3">
-        <v>42400</v>
+        <v>43600</v>
       </c>
       <c r="K41" s="3">
         <v>31500</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>265000</v>
+        <v>272500</v>
       </c>
       <c r="E42" s="3">
-        <v>292400</v>
+        <v>300700</v>
       </c>
       <c r="F42" s="3">
-        <v>428100</v>
+        <v>440200</v>
       </c>
       <c r="G42" s="3">
-        <v>388500</v>
+        <v>399500</v>
       </c>
       <c r="H42" s="3">
-        <v>110300</v>
+        <v>113500</v>
       </c>
       <c r="I42" s="3">
-        <v>91900</v>
+        <v>94500</v>
       </c>
       <c r="J42" s="3">
-        <v>116500</v>
+        <v>119800</v>
       </c>
       <c r="K42" s="3">
         <v>190800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>380900</v>
+        <v>391700</v>
       </c>
       <c r="E43" s="3">
-        <v>355200</v>
+        <v>365200</v>
       </c>
       <c r="F43" s="3">
-        <v>304400</v>
+        <v>313000</v>
       </c>
       <c r="G43" s="3">
-        <v>218700</v>
+        <v>224900</v>
       </c>
       <c r="H43" s="3">
-        <v>224600</v>
+        <v>231000</v>
       </c>
       <c r="I43" s="3">
-        <v>188100</v>
+        <v>193400</v>
       </c>
       <c r="J43" s="3">
-        <v>200100</v>
+        <v>205800</v>
       </c>
       <c r="K43" s="3">
         <v>213800</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>247000</v>
+        <v>254000</v>
       </c>
       <c r="E44" s="3">
-        <v>260600</v>
+        <v>268000</v>
       </c>
       <c r="F44" s="3">
-        <v>202800</v>
+        <v>208600</v>
       </c>
       <c r="G44" s="3">
-        <v>135700</v>
+        <v>139500</v>
       </c>
       <c r="H44" s="3">
-        <v>156500</v>
+        <v>160900</v>
       </c>
       <c r="I44" s="3">
-        <v>160400</v>
+        <v>164900</v>
       </c>
       <c r="J44" s="3">
-        <v>139200</v>
+        <v>143200</v>
       </c>
       <c r="K44" s="3">
         <v>163500</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>20600</v>
+        <v>21200</v>
       </c>
       <c r="E45" s="3">
-        <v>208000</v>
+        <v>213900</v>
       </c>
       <c r="F45" s="3">
-        <v>14500</v>
+        <v>14900</v>
       </c>
       <c r="G45" s="3">
-        <v>13900</v>
+        <v>14300</v>
       </c>
       <c r="H45" s="3">
-        <v>17300</v>
+        <v>17800</v>
       </c>
       <c r="I45" s="3">
-        <v>16200</v>
+        <v>16600</v>
       </c>
       <c r="J45" s="3">
-        <v>14800</v>
+        <v>15200</v>
       </c>
       <c r="K45" s="3">
         <v>24900</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1040700</v>
+        <v>1070100</v>
       </c>
       <c r="E46" s="3">
-        <v>1231400</v>
+        <v>1266300</v>
       </c>
       <c r="F46" s="3">
-        <v>1050400</v>
+        <v>1080200</v>
       </c>
       <c r="G46" s="3">
-        <v>845100</v>
+        <v>869100</v>
       </c>
       <c r="H46" s="3">
-        <v>565500</v>
+        <v>581500</v>
       </c>
       <c r="I46" s="3">
-        <v>510500</v>
+        <v>524900</v>
       </c>
       <c r="J46" s="3">
-        <v>513100</v>
+        <v>527600</v>
       </c>
       <c r="K46" s="3">
         <v>624600</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>154700</v>
+        <v>159100</v>
       </c>
       <c r="E47" s="3">
-        <v>162700</v>
+        <v>167300</v>
       </c>
       <c r="F47" s="3">
-        <v>154400</v>
+        <v>158800</v>
       </c>
       <c r="G47" s="3">
-        <v>175600</v>
+        <v>180600</v>
       </c>
       <c r="H47" s="3">
-        <v>217800</v>
+        <v>223900</v>
       </c>
       <c r="I47" s="3">
-        <v>124100</v>
+        <v>127600</v>
       </c>
       <c r="J47" s="3">
-        <v>97100</v>
+        <v>99900</v>
       </c>
       <c r="K47" s="3">
         <v>94700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>924700</v>
+        <v>950900</v>
       </c>
       <c r="E48" s="3">
-        <v>846100</v>
+        <v>870100</v>
       </c>
       <c r="F48" s="3">
-        <v>759400</v>
+        <v>780900</v>
       </c>
       <c r="G48" s="3">
-        <v>641900</v>
+        <v>660100</v>
       </c>
       <c r="H48" s="3">
-        <v>766100</v>
+        <v>787800</v>
       </c>
       <c r="I48" s="3">
-        <v>753400</v>
+        <v>774700</v>
       </c>
       <c r="J48" s="3">
-        <v>699300</v>
+        <v>719100</v>
       </c>
       <c r="K48" s="3">
         <v>752800</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>867100</v>
+        <v>891700</v>
       </c>
       <c r="E49" s="3">
-        <v>848900</v>
+        <v>872900</v>
       </c>
       <c r="F49" s="3">
-        <v>824300</v>
+        <v>847700</v>
       </c>
       <c r="G49" s="3">
-        <v>745000</v>
+        <v>766100</v>
       </c>
       <c r="H49" s="3">
-        <v>844100</v>
+        <v>868000</v>
       </c>
       <c r="I49" s="3">
-        <v>833200</v>
+        <v>856800</v>
       </c>
       <c r="J49" s="3">
-        <v>802300</v>
+        <v>825000</v>
       </c>
       <c r="K49" s="3">
         <v>885800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>109600</v>
+        <v>112700</v>
       </c>
       <c r="E52" s="3">
-        <v>102300</v>
+        <v>105200</v>
       </c>
       <c r="F52" s="3">
-        <v>334300</v>
+        <v>343800</v>
       </c>
       <c r="G52" s="3">
-        <v>187300</v>
+        <v>192600</v>
       </c>
       <c r="H52" s="3">
-        <v>141000</v>
+        <v>145000</v>
       </c>
       <c r="I52" s="3">
-        <v>126200</v>
+        <v>129700</v>
       </c>
       <c r="J52" s="3">
-        <v>129900</v>
+        <v>133600</v>
       </c>
       <c r="K52" s="3">
         <v>127100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3096800</v>
+        <v>3184500</v>
       </c>
       <c r="E54" s="3">
-        <v>3191300</v>
+        <v>3281700</v>
       </c>
       <c r="F54" s="3">
-        <v>3122900</v>
+        <v>3211300</v>
       </c>
       <c r="G54" s="3">
-        <v>2594900</v>
+        <v>2668400</v>
       </c>
       <c r="H54" s="3">
-        <v>2534400</v>
+        <v>2606100</v>
       </c>
       <c r="I54" s="3">
-        <v>2347400</v>
+        <v>2413800</v>
       </c>
       <c r="J54" s="3">
-        <v>2241800</v>
+        <v>2305200</v>
       </c>
       <c r="K54" s="3">
         <v>2485000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>556500</v>
+        <v>572200</v>
       </c>
       <c r="E57" s="3">
-        <v>503600</v>
+        <v>517800</v>
       </c>
       <c r="F57" s="3">
-        <v>406500</v>
+        <v>418000</v>
       </c>
       <c r="G57" s="3">
-        <v>286200</v>
+        <v>294300</v>
       </c>
       <c r="H57" s="3">
-        <v>315200</v>
+        <v>324100</v>
       </c>
       <c r="I57" s="3">
-        <v>301000</v>
+        <v>309500</v>
       </c>
       <c r="J57" s="3">
-        <v>309000</v>
+        <v>317700</v>
       </c>
       <c r="K57" s="3">
         <v>324300</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>41200</v>
+        <v>42400</v>
       </c>
       <c r="E58" s="3">
-        <v>369500</v>
+        <v>379900</v>
       </c>
       <c r="F58" s="3">
-        <v>35600</v>
+        <v>36600</v>
       </c>
       <c r="G58" s="3">
-        <v>26700</v>
+        <v>27500</v>
       </c>
       <c r="H58" s="3">
-        <v>30800</v>
+        <v>31700</v>
       </c>
       <c r="I58" s="3">
-        <v>46400</v>
+        <v>47700</v>
       </c>
       <c r="J58" s="3">
-        <v>56900</v>
+        <v>58500</v>
       </c>
       <c r="K58" s="3">
         <v>56600</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>136700</v>
+        <v>140600</v>
       </c>
       <c r="E59" s="3">
-        <v>133200</v>
+        <v>136900</v>
       </c>
       <c r="F59" s="3">
-        <v>119200</v>
+        <v>122600</v>
       </c>
       <c r="G59" s="3">
-        <v>87800</v>
+        <v>90300</v>
       </c>
       <c r="H59" s="3">
-        <v>90400</v>
+        <v>92900</v>
       </c>
       <c r="I59" s="3">
-        <v>97700</v>
+        <v>100500</v>
       </c>
       <c r="J59" s="3">
-        <v>88100</v>
+        <v>90600</v>
       </c>
       <c r="K59" s="3">
         <v>93200</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>734400</v>
+        <v>755200</v>
       </c>
       <c r="E60" s="3">
-        <v>1006200</v>
+        <v>1034700</v>
       </c>
       <c r="F60" s="3">
-        <v>561300</v>
+        <v>577200</v>
       </c>
       <c r="G60" s="3">
-        <v>400700</v>
+        <v>412100</v>
       </c>
       <c r="H60" s="3">
-        <v>436400</v>
+        <v>448700</v>
       </c>
       <c r="I60" s="3">
-        <v>445100</v>
+        <v>457600</v>
       </c>
       <c r="J60" s="3">
-        <v>454000</v>
+        <v>466800</v>
       </c>
       <c r="K60" s="3">
         <v>474100</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1051400</v>
+        <v>1081100</v>
       </c>
       <c r="E61" s="3">
-        <v>840200</v>
+        <v>864000</v>
       </c>
       <c r="F61" s="3">
-        <v>1103500</v>
+        <v>1134700</v>
       </c>
       <c r="G61" s="3">
-        <v>994600</v>
+        <v>1022700</v>
       </c>
       <c r="H61" s="3">
-        <v>787900</v>
+        <v>810200</v>
       </c>
       <c r="I61" s="3">
-        <v>759600</v>
+        <v>781100</v>
       </c>
       <c r="J61" s="3">
-        <v>716300</v>
+        <v>736600</v>
       </c>
       <c r="K61" s="3">
         <v>815400</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>334700</v>
+        <v>344200</v>
       </c>
       <c r="E62" s="3">
-        <v>408600</v>
+        <v>420100</v>
       </c>
       <c r="F62" s="3">
-        <v>290500</v>
+        <v>298700</v>
       </c>
       <c r="G62" s="3">
-        <v>318200</v>
+        <v>327200</v>
       </c>
       <c r="H62" s="3">
-        <v>283100</v>
+        <v>291100</v>
       </c>
       <c r="I62" s="3">
-        <v>227200</v>
+        <v>233700</v>
       </c>
       <c r="J62" s="3">
-        <v>209400</v>
+        <v>215400</v>
       </c>
       <c r="K62" s="3">
         <v>243900</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2157300</v>
+        <v>2218400</v>
       </c>
       <c r="E66" s="3">
-        <v>2284800</v>
+        <v>2349400</v>
       </c>
       <c r="F66" s="3">
-        <v>1982200</v>
+        <v>2038300</v>
       </c>
       <c r="G66" s="3">
-        <v>1735100</v>
+        <v>1784200</v>
       </c>
       <c r="H66" s="3">
-        <v>1528800</v>
+        <v>1572100</v>
       </c>
       <c r="I66" s="3">
-        <v>1452900</v>
+        <v>1494100</v>
       </c>
       <c r="J66" s="3">
-        <v>1403000</v>
+        <v>1442700</v>
       </c>
       <c r="K66" s="3">
         <v>1557700</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1274600</v>
+        <v>1310700</v>
       </c>
       <c r="E72" s="3">
-        <v>1219100</v>
+        <v>1253600</v>
       </c>
       <c r="F72" s="3">
-        <v>1273300</v>
+        <v>1309400</v>
       </c>
       <c r="G72" s="3">
-        <v>1152600</v>
+        <v>1185200</v>
       </c>
       <c r="H72" s="3">
-        <v>1096100</v>
+        <v>1127100</v>
       </c>
       <c r="I72" s="3">
-        <v>949100</v>
+        <v>976000</v>
       </c>
       <c r="J72" s="3">
-        <v>808400</v>
+        <v>831300</v>
       </c>
       <c r="K72" s="3">
         <v>816800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>939500</v>
+        <v>966100</v>
       </c>
       <c r="E76" s="3">
-        <v>906600</v>
+        <v>932200</v>
       </c>
       <c r="F76" s="3">
-        <v>1140700</v>
+        <v>1173000</v>
       </c>
       <c r="G76" s="3">
-        <v>859900</v>
+        <v>884200</v>
       </c>
       <c r="H76" s="3">
-        <v>1005600</v>
+        <v>1034000</v>
       </c>
       <c r="I76" s="3">
-        <v>894400</v>
+        <v>919800</v>
       </c>
       <c r="J76" s="3">
-        <v>838800</v>
+        <v>862500</v>
       </c>
       <c r="K76" s="3">
         <v>927300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>181700</v>
+        <v>186900</v>
       </c>
       <c r="E81" s="3">
+        <v>136800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>168600</v>
+      </c>
+      <c r="G81" s="3">
         <v>133000</v>
       </c>
-      <c r="F81" s="3">
-        <v>164000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>129300</v>
-      </c>
       <c r="H81" s="3">
-        <v>184100</v>
+        <v>189400</v>
       </c>
       <c r="I81" s="3">
-        <v>102400</v>
+        <v>105300</v>
       </c>
       <c r="J81" s="3">
-        <v>124900</v>
+        <v>128400</v>
       </c>
       <c r="K81" s="3">
         <v>102300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>374000</v>
+        <v>384600</v>
       </c>
       <c r="E89" s="3">
-        <v>403700</v>
+        <v>415100</v>
       </c>
       <c r="F89" s="3">
-        <v>316800</v>
+        <v>325700</v>
       </c>
       <c r="G89" s="3">
-        <v>293000</v>
+        <v>301200</v>
       </c>
       <c r="H89" s="3">
-        <v>268300</v>
+        <v>275900</v>
       </c>
       <c r="I89" s="3">
-        <v>244300</v>
+        <v>251200</v>
       </c>
       <c r="J89" s="3">
-        <v>262800</v>
+        <v>270300</v>
       </c>
       <c r="K89" s="3">
         <v>252500</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-204300</v>
+        <v>-210100</v>
       </c>
       <c r="E91" s="3">
-        <v>-197900</v>
+        <v>-203500</v>
       </c>
       <c r="F91" s="3">
-        <v>-147200</v>
+        <v>-151400</v>
       </c>
       <c r="G91" s="3">
-        <v>-91000</v>
+        <v>-93600</v>
       </c>
       <c r="H91" s="3">
-        <v>-117300</v>
+        <v>-120600</v>
       </c>
       <c r="I91" s="3">
-        <v>-128300</v>
+        <v>-132000</v>
       </c>
       <c r="J91" s="3">
-        <v>-179000</v>
+        <v>-184100</v>
       </c>
       <c r="K91" s="3">
         <v>-144900</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-167800</v>
+        <v>-172500</v>
       </c>
       <c r="E94" s="3">
-        <v>-90300</v>
+        <v>-92800</v>
       </c>
       <c r="F94" s="3">
-        <v>-210100</v>
+        <v>-216100</v>
       </c>
       <c r="G94" s="3">
-        <v>-237300</v>
+        <v>-244000</v>
       </c>
       <c r="H94" s="3">
-        <v>-116700</v>
+        <v>-120000</v>
       </c>
       <c r="I94" s="3">
-        <v>-125200</v>
+        <v>-128700</v>
       </c>
       <c r="J94" s="3">
-        <v>-179000</v>
+        <v>-184000</v>
       </c>
       <c r="K94" s="3">
         <v>-128700</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-175800</v>
+        <v>-180800</v>
       </c>
       <c r="E96" s="3">
-        <v>-290800</v>
+        <v>-299000</v>
       </c>
       <c r="F96" s="3">
-        <v>-112700</v>
+        <v>-115900</v>
       </c>
       <c r="G96" s="3">
-        <v>-106000</v>
+        <v>-109000</v>
       </c>
       <c r="H96" s="3">
-        <v>-91400</v>
+        <v>-94000</v>
       </c>
       <c r="I96" s="3">
-        <v>-92800</v>
+        <v>-95400</v>
       </c>
       <c r="J96" s="3">
-        <v>-79500</v>
+        <v>-81700</v>
       </c>
       <c r="K96" s="3">
         <v>-76400</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-198400</v>
+        <v>-204000</v>
       </c>
       <c r="E100" s="3">
-        <v>-304200</v>
+        <v>-312800</v>
       </c>
       <c r="F100" s="3">
-        <v>-122200</v>
+        <v>-125700</v>
       </c>
       <c r="G100" s="3">
-        <v>119800</v>
+        <v>123200</v>
       </c>
       <c r="H100" s="3">
-        <v>-134700</v>
+        <v>-138600</v>
       </c>
       <c r="I100" s="3">
-        <v>-121500</v>
+        <v>-125000</v>
       </c>
       <c r="J100" s="3">
-        <v>-83000</v>
+        <v>-85400</v>
       </c>
       <c r="K100" s="3">
         <v>-111000</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="E101" s="3">
-        <v>-22600</v>
+        <v>-23300</v>
       </c>
       <c r="F101" s="3">
-        <v>10100</v>
+        <v>10400</v>
       </c>
       <c r="G101" s="3">
-        <v>-14400</v>
+        <v>-14800</v>
       </c>
       <c r="H101" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="I101" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="J101" s="3">
-        <v>-6200</v>
+        <v>-6300</v>
       </c>
       <c r="K101" s="3">
         <v>900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>12700</v>
+        <v>13100</v>
       </c>
       <c r="E102" s="3">
-        <v>-13400</v>
+        <v>-13800</v>
       </c>
       <c r="F102" s="3">
-        <v>-5500</v>
+        <v>-5700</v>
       </c>
       <c r="G102" s="3">
-        <v>161100</v>
+        <v>165600</v>
       </c>
       <c r="H102" s="3">
-        <v>21200</v>
+        <v>21800</v>
       </c>
       <c r="I102" s="3">
         <v>1400</v>
       </c>
       <c r="J102" s="3">
-        <v>-5300</v>
+        <v>-5500</v>
       </c>
       <c r="K102" s="3">
         <v>13700</v>

--- a/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2854100</v>
+        <v>2827900</v>
       </c>
       <c r="E8" s="3">
-        <v>2896000</v>
+        <v>2869400</v>
       </c>
       <c r="F8" s="3">
-        <v>2416200</v>
+        <v>2394100</v>
       </c>
       <c r="G8" s="3">
-        <v>1851100</v>
+        <v>1834100</v>
       </c>
       <c r="H8" s="3">
-        <v>1939100</v>
+        <v>1921300</v>
       </c>
       <c r="I8" s="3">
-        <v>1823500</v>
+        <v>1806700</v>
       </c>
       <c r="J8" s="3">
-        <v>2015300</v>
+        <v>1996800</v>
       </c>
       <c r="K8" s="3">
         <v>2008500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1746200</v>
+        <v>1730200</v>
       </c>
       <c r="E9" s="3">
-        <v>1775300</v>
+        <v>1759000</v>
       </c>
       <c r="F9" s="3">
-        <v>1499200</v>
+        <v>1485400</v>
       </c>
       <c r="G9" s="3">
-        <v>1114500</v>
+        <v>1104300</v>
       </c>
       <c r="H9" s="3">
-        <v>1142700</v>
+        <v>1132200</v>
       </c>
       <c r="I9" s="3">
-        <v>1055200</v>
+        <v>1045500</v>
       </c>
       <c r="J9" s="3">
-        <v>1165200</v>
+        <v>1154500</v>
       </c>
       <c r="K9" s="3">
         <v>1168300</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1107900</v>
+        <v>1097800</v>
       </c>
       <c r="E10" s="3">
-        <v>1120700</v>
+        <v>1110400</v>
       </c>
       <c r="F10" s="3">
-        <v>917100</v>
+        <v>908600</v>
       </c>
       <c r="G10" s="3">
-        <v>736600</v>
+        <v>729800</v>
       </c>
       <c r="H10" s="3">
-        <v>796400</v>
+        <v>789100</v>
       </c>
       <c r="I10" s="3">
-        <v>768300</v>
+        <v>761300</v>
       </c>
       <c r="J10" s="3">
-        <v>850000</v>
+        <v>842200</v>
       </c>
       <c r="K10" s="3">
         <v>840200</v>
@@ -970,16 +970,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>29100</v>
+        <v>28800</v>
       </c>
       <c r="E14" s="3">
-        <v>25200</v>
+        <v>25000</v>
       </c>
       <c r="F14" s="3">
         <v>500</v>
       </c>
       <c r="G14" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="H14" s="3">
         <v>3200</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2509300</v>
+        <v>2486300</v>
       </c>
       <c r="E17" s="3">
-        <v>2545300</v>
+        <v>2521900</v>
       </c>
       <c r="F17" s="3">
-        <v>2112600</v>
+        <v>2093200</v>
       </c>
       <c r="G17" s="3">
-        <v>1599800</v>
+        <v>1585200</v>
       </c>
       <c r="H17" s="3">
-        <v>1663900</v>
+        <v>1648600</v>
       </c>
       <c r="I17" s="3">
-        <v>1595400</v>
+        <v>1580800</v>
       </c>
       <c r="J17" s="3">
-        <v>1775400</v>
+        <v>1759100</v>
       </c>
       <c r="K17" s="3">
         <v>1794600</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>344800</v>
+        <v>341600</v>
       </c>
       <c r="E18" s="3">
-        <v>350700</v>
+        <v>347500</v>
       </c>
       <c r="F18" s="3">
-        <v>303600</v>
+        <v>300800</v>
       </c>
       <c r="G18" s="3">
-        <v>251300</v>
+        <v>249000</v>
       </c>
       <c r="H18" s="3">
-        <v>275300</v>
+        <v>272800</v>
       </c>
       <c r="I18" s="3">
-        <v>228000</v>
+        <v>226000</v>
       </c>
       <c r="J18" s="3">
-        <v>239800</v>
+        <v>237600</v>
       </c>
       <c r="K18" s="3">
         <v>213900</v>
@@ -1185,22 +1185,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="E20" s="3">
-        <v>-36200</v>
+        <v>-35900</v>
       </c>
       <c r="F20" s="3">
-        <v>-26900</v>
+        <v>-26600</v>
       </c>
       <c r="G20" s="3">
-        <v>-5900</v>
+        <v>-5800</v>
       </c>
       <c r="H20" s="3">
-        <v>25500</v>
+        <v>25200</v>
       </c>
       <c r="I20" s="3">
-        <v>-17200</v>
+        <v>-17100</v>
       </c>
       <c r="J20" s="3">
         <v>-1600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>349700</v>
+        <v>346400</v>
       </c>
       <c r="E21" s="3">
-        <v>314500</v>
+        <v>311600</v>
       </c>
       <c r="F21" s="3">
-        <v>276800</v>
+        <v>274200</v>
       </c>
       <c r="G21" s="3">
-        <v>245400</v>
+        <v>243100</v>
       </c>
       <c r="H21" s="3">
-        <v>300700</v>
+        <v>298000</v>
       </c>
       <c r="I21" s="3">
-        <v>210800</v>
+        <v>208900</v>
       </c>
       <c r="J21" s="3">
-        <v>238200</v>
+        <v>236000</v>
       </c>
       <c r="K21" s="3">
         <v>210700</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>65700</v>
+        <v>65100</v>
       </c>
       <c r="E22" s="3">
-        <v>60800</v>
+        <v>60200</v>
       </c>
       <c r="F22" s="3">
-        <v>55300</v>
+        <v>54800</v>
       </c>
       <c r="G22" s="3">
-        <v>51400</v>
+        <v>50900</v>
       </c>
       <c r="H22" s="3">
-        <v>43000</v>
+        <v>42600</v>
       </c>
       <c r="I22" s="3">
-        <v>44000</v>
+        <v>43600</v>
       </c>
       <c r="J22" s="3">
-        <v>52000</v>
+        <v>51600</v>
       </c>
       <c r="K22" s="3">
         <v>51600</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>284000</v>
+        <v>281300</v>
       </c>
       <c r="E23" s="3">
-        <v>253800</v>
+        <v>251400</v>
       </c>
       <c r="F23" s="3">
-        <v>221500</v>
+        <v>219500</v>
       </c>
       <c r="G23" s="3">
-        <v>194000</v>
+        <v>192300</v>
       </c>
       <c r="H23" s="3">
-        <v>257700</v>
+        <v>255300</v>
       </c>
       <c r="I23" s="3">
-        <v>166800</v>
+        <v>165300</v>
       </c>
       <c r="J23" s="3">
-        <v>186200</v>
+        <v>184500</v>
       </c>
       <c r="K23" s="3">
         <v>159200</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>93700</v>
+        <v>92900</v>
       </c>
       <c r="E24" s="3">
-        <v>113700</v>
+        <v>112700</v>
       </c>
       <c r="F24" s="3">
-        <v>50300</v>
+        <v>49900</v>
       </c>
       <c r="G24" s="3">
-        <v>59800</v>
+        <v>59300</v>
       </c>
       <c r="H24" s="3">
-        <v>66700</v>
+        <v>66100</v>
       </c>
       <c r="I24" s="3">
-        <v>60600</v>
+        <v>60000</v>
       </c>
       <c r="J24" s="3">
-        <v>56500</v>
+        <v>55900</v>
       </c>
       <c r="K24" s="3">
         <v>55200</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>190200</v>
+        <v>188500</v>
       </c>
       <c r="E26" s="3">
-        <v>140000</v>
+        <v>138700</v>
       </c>
       <c r="F26" s="3">
-        <v>171200</v>
+        <v>169600</v>
       </c>
       <c r="G26" s="3">
-        <v>134200</v>
+        <v>133000</v>
       </c>
       <c r="H26" s="3">
-        <v>191000</v>
+        <v>189300</v>
       </c>
       <c r="I26" s="3">
-        <v>106200</v>
+        <v>105200</v>
       </c>
       <c r="J26" s="3">
-        <v>129700</v>
+        <v>128500</v>
       </c>
       <c r="K26" s="3">
         <v>104000</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>186900</v>
+        <v>185200</v>
       </c>
       <c r="E27" s="3">
-        <v>136800</v>
+        <v>135500</v>
       </c>
       <c r="F27" s="3">
-        <v>168600</v>
+        <v>167100</v>
       </c>
       <c r="G27" s="3">
-        <v>133000</v>
+        <v>131800</v>
       </c>
       <c r="H27" s="3">
-        <v>189400</v>
+        <v>187600</v>
       </c>
       <c r="I27" s="3">
-        <v>105300</v>
+        <v>104300</v>
       </c>
       <c r="J27" s="3">
-        <v>128400</v>
+        <v>127300</v>
       </c>
       <c r="K27" s="3">
         <v>102300</v>
@@ -1725,22 +1725,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4900</v>
+        <v>-4800</v>
       </c>
       <c r="E32" s="3">
-        <v>36200</v>
+        <v>35900</v>
       </c>
       <c r="F32" s="3">
-        <v>26900</v>
+        <v>26600</v>
       </c>
       <c r="G32" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="H32" s="3">
-        <v>-25500</v>
+        <v>-25200</v>
       </c>
       <c r="I32" s="3">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="J32" s="3">
         <v>1600</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>186900</v>
+        <v>185200</v>
       </c>
       <c r="E33" s="3">
-        <v>136800</v>
+        <v>135500</v>
       </c>
       <c r="F33" s="3">
-        <v>168600</v>
+        <v>167100</v>
       </c>
       <c r="G33" s="3">
-        <v>133000</v>
+        <v>131800</v>
       </c>
       <c r="H33" s="3">
-        <v>189400</v>
+        <v>187600</v>
       </c>
       <c r="I33" s="3">
-        <v>105300</v>
+        <v>104300</v>
       </c>
       <c r="J33" s="3">
-        <v>128400</v>
+        <v>127300</v>
       </c>
       <c r="K33" s="3">
         <v>102300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>186900</v>
+        <v>185200</v>
       </c>
       <c r="E35" s="3">
-        <v>136800</v>
+        <v>135500</v>
       </c>
       <c r="F35" s="3">
-        <v>168600</v>
+        <v>167100</v>
       </c>
       <c r="G35" s="3">
-        <v>133000</v>
+        <v>131800</v>
       </c>
       <c r="H35" s="3">
-        <v>189400</v>
+        <v>187600</v>
       </c>
       <c r="I35" s="3">
-        <v>105300</v>
+        <v>104300</v>
       </c>
       <c r="J35" s="3">
-        <v>128400</v>
+        <v>127300</v>
       </c>
       <c r="K35" s="3">
         <v>102300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>130700</v>
+        <v>129500</v>
       </c>
       <c r="E41" s="3">
-        <v>118500</v>
+        <v>117400</v>
       </c>
       <c r="F41" s="3">
-        <v>103500</v>
+        <v>102600</v>
       </c>
       <c r="G41" s="3">
-        <v>90800</v>
+        <v>90000</v>
       </c>
       <c r="H41" s="3">
-        <v>58300</v>
+        <v>57800</v>
       </c>
       <c r="I41" s="3">
-        <v>55400</v>
+        <v>54900</v>
       </c>
       <c r="J41" s="3">
-        <v>43600</v>
+        <v>43200</v>
       </c>
       <c r="K41" s="3">
         <v>31500</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>272500</v>
+        <v>270000</v>
       </c>
       <c r="E42" s="3">
-        <v>300700</v>
+        <v>297900</v>
       </c>
       <c r="F42" s="3">
-        <v>440200</v>
+        <v>436200</v>
       </c>
       <c r="G42" s="3">
-        <v>399500</v>
+        <v>395800</v>
       </c>
       <c r="H42" s="3">
-        <v>113500</v>
+        <v>112400</v>
       </c>
       <c r="I42" s="3">
-        <v>94500</v>
+        <v>93700</v>
       </c>
       <c r="J42" s="3">
-        <v>119800</v>
+        <v>118700</v>
       </c>
       <c r="K42" s="3">
         <v>190800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>391700</v>
+        <v>388100</v>
       </c>
       <c r="E43" s="3">
-        <v>365200</v>
+        <v>361900</v>
       </c>
       <c r="F43" s="3">
-        <v>313000</v>
+        <v>310100</v>
       </c>
       <c r="G43" s="3">
-        <v>224900</v>
+        <v>222900</v>
       </c>
       <c r="H43" s="3">
-        <v>231000</v>
+        <v>228900</v>
       </c>
       <c r="I43" s="3">
-        <v>193400</v>
+        <v>191600</v>
       </c>
       <c r="J43" s="3">
-        <v>205800</v>
+        <v>203900</v>
       </c>
       <c r="K43" s="3">
         <v>213800</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>254000</v>
+        <v>251700</v>
       </c>
       <c r="E44" s="3">
-        <v>268000</v>
+        <v>265600</v>
       </c>
       <c r="F44" s="3">
-        <v>208600</v>
+        <v>206700</v>
       </c>
       <c r="G44" s="3">
-        <v>139500</v>
+        <v>138200</v>
       </c>
       <c r="H44" s="3">
-        <v>160900</v>
+        <v>159500</v>
       </c>
       <c r="I44" s="3">
-        <v>164900</v>
+        <v>163400</v>
       </c>
       <c r="J44" s="3">
-        <v>143200</v>
+        <v>141900</v>
       </c>
       <c r="K44" s="3">
         <v>163500</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>21200</v>
+        <v>21000</v>
       </c>
       <c r="E45" s="3">
-        <v>213900</v>
+        <v>212000</v>
       </c>
       <c r="F45" s="3">
-        <v>14900</v>
+        <v>14800</v>
       </c>
       <c r="G45" s="3">
-        <v>14300</v>
+        <v>14200</v>
       </c>
       <c r="H45" s="3">
-        <v>17800</v>
+        <v>17600</v>
       </c>
       <c r="I45" s="3">
-        <v>16600</v>
+        <v>16500</v>
       </c>
       <c r="J45" s="3">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="K45" s="3">
         <v>24900</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1070100</v>
+        <v>1060300</v>
       </c>
       <c r="E46" s="3">
-        <v>1266300</v>
+        <v>1254700</v>
       </c>
       <c r="F46" s="3">
-        <v>1080200</v>
+        <v>1070300</v>
       </c>
       <c r="G46" s="3">
-        <v>869100</v>
+        <v>861100</v>
       </c>
       <c r="H46" s="3">
-        <v>581500</v>
+        <v>576200</v>
       </c>
       <c r="I46" s="3">
-        <v>524900</v>
+        <v>520100</v>
       </c>
       <c r="J46" s="3">
-        <v>527600</v>
+        <v>522700</v>
       </c>
       <c r="K46" s="3">
         <v>624600</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>159100</v>
+        <v>157700</v>
       </c>
       <c r="E47" s="3">
-        <v>167300</v>
+        <v>165700</v>
       </c>
       <c r="F47" s="3">
-        <v>158800</v>
+        <v>157300</v>
       </c>
       <c r="G47" s="3">
-        <v>180600</v>
+        <v>178900</v>
       </c>
       <c r="H47" s="3">
-        <v>223900</v>
+        <v>221900</v>
       </c>
       <c r="I47" s="3">
-        <v>127600</v>
+        <v>126400</v>
       </c>
       <c r="J47" s="3">
-        <v>99900</v>
+        <v>99000</v>
       </c>
       <c r="K47" s="3">
         <v>94700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>950900</v>
+        <v>942200</v>
       </c>
       <c r="E48" s="3">
-        <v>870100</v>
+        <v>862100</v>
       </c>
       <c r="F48" s="3">
-        <v>780900</v>
+        <v>773700</v>
       </c>
       <c r="G48" s="3">
-        <v>660100</v>
+        <v>654000</v>
       </c>
       <c r="H48" s="3">
-        <v>787800</v>
+        <v>780500</v>
       </c>
       <c r="I48" s="3">
-        <v>774700</v>
+        <v>767600</v>
       </c>
       <c r="J48" s="3">
-        <v>719100</v>
+        <v>712500</v>
       </c>
       <c r="K48" s="3">
         <v>752800</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>891700</v>
+        <v>883500</v>
       </c>
       <c r="E49" s="3">
-        <v>872900</v>
+        <v>864900</v>
       </c>
       <c r="F49" s="3">
-        <v>847700</v>
+        <v>839900</v>
       </c>
       <c r="G49" s="3">
-        <v>766100</v>
+        <v>759100</v>
       </c>
       <c r="H49" s="3">
-        <v>868000</v>
+        <v>860000</v>
       </c>
       <c r="I49" s="3">
-        <v>856800</v>
+        <v>848900</v>
       </c>
       <c r="J49" s="3">
-        <v>825000</v>
+        <v>817400</v>
       </c>
       <c r="K49" s="3">
         <v>885800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>112700</v>
+        <v>111600</v>
       </c>
       <c r="E52" s="3">
-        <v>105200</v>
+        <v>104200</v>
       </c>
       <c r="F52" s="3">
-        <v>343800</v>
+        <v>340600</v>
       </c>
       <c r="G52" s="3">
-        <v>192600</v>
+        <v>190800</v>
       </c>
       <c r="H52" s="3">
-        <v>145000</v>
+        <v>143700</v>
       </c>
       <c r="I52" s="3">
-        <v>129700</v>
+        <v>128500</v>
       </c>
       <c r="J52" s="3">
-        <v>133600</v>
+        <v>132400</v>
       </c>
       <c r="K52" s="3">
         <v>127100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3184500</v>
+        <v>3155200</v>
       </c>
       <c r="E54" s="3">
-        <v>3281700</v>
+        <v>3251600</v>
       </c>
       <c r="F54" s="3">
-        <v>3211300</v>
+        <v>3181800</v>
       </c>
       <c r="G54" s="3">
-        <v>2668400</v>
+        <v>2643900</v>
       </c>
       <c r="H54" s="3">
-        <v>2606100</v>
+        <v>2582200</v>
       </c>
       <c r="I54" s="3">
-        <v>2413800</v>
+        <v>2391700</v>
       </c>
       <c r="J54" s="3">
-        <v>2305200</v>
+        <v>2284000</v>
       </c>
       <c r="K54" s="3">
         <v>2485000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>572200</v>
+        <v>567000</v>
       </c>
       <c r="E57" s="3">
-        <v>517800</v>
+        <v>513100</v>
       </c>
       <c r="F57" s="3">
-        <v>418000</v>
+        <v>414200</v>
       </c>
       <c r="G57" s="3">
-        <v>294300</v>
+        <v>291600</v>
       </c>
       <c r="H57" s="3">
-        <v>324100</v>
+        <v>321100</v>
       </c>
       <c r="I57" s="3">
-        <v>309500</v>
+        <v>306700</v>
       </c>
       <c r="J57" s="3">
-        <v>317700</v>
+        <v>314800</v>
       </c>
       <c r="K57" s="3">
         <v>324300</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>42400</v>
+        <v>42000</v>
       </c>
       <c r="E58" s="3">
-        <v>379900</v>
+        <v>376400</v>
       </c>
       <c r="F58" s="3">
-        <v>36600</v>
+        <v>36300</v>
       </c>
       <c r="G58" s="3">
-        <v>27500</v>
+        <v>27200</v>
       </c>
       <c r="H58" s="3">
-        <v>31700</v>
+        <v>31400</v>
       </c>
       <c r="I58" s="3">
-        <v>47700</v>
+        <v>47200</v>
       </c>
       <c r="J58" s="3">
-        <v>58500</v>
+        <v>58000</v>
       </c>
       <c r="K58" s="3">
         <v>56600</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>140600</v>
+        <v>139300</v>
       </c>
       <c r="E59" s="3">
-        <v>136900</v>
+        <v>135700</v>
       </c>
       <c r="F59" s="3">
-        <v>122600</v>
+        <v>121400</v>
       </c>
       <c r="G59" s="3">
-        <v>90300</v>
+        <v>89500</v>
       </c>
       <c r="H59" s="3">
-        <v>92900</v>
+        <v>92100</v>
       </c>
       <c r="I59" s="3">
-        <v>100500</v>
+        <v>99600</v>
       </c>
       <c r="J59" s="3">
-        <v>90600</v>
+        <v>89800</v>
       </c>
       <c r="K59" s="3">
         <v>93200</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>755200</v>
+        <v>748300</v>
       </c>
       <c r="E60" s="3">
-        <v>1034700</v>
+        <v>1025200</v>
       </c>
       <c r="F60" s="3">
-        <v>577200</v>
+        <v>571900</v>
       </c>
       <c r="G60" s="3">
-        <v>412100</v>
+        <v>408300</v>
       </c>
       <c r="H60" s="3">
-        <v>448700</v>
+        <v>444600</v>
       </c>
       <c r="I60" s="3">
-        <v>457600</v>
+        <v>453500</v>
       </c>
       <c r="J60" s="3">
-        <v>466800</v>
+        <v>462600</v>
       </c>
       <c r="K60" s="3">
         <v>474100</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1081100</v>
+        <v>1071200</v>
       </c>
       <c r="E61" s="3">
-        <v>864000</v>
+        <v>856000</v>
       </c>
       <c r="F61" s="3">
-        <v>1134700</v>
+        <v>1124300</v>
       </c>
       <c r="G61" s="3">
-        <v>1022700</v>
+        <v>1013300</v>
       </c>
       <c r="H61" s="3">
-        <v>810200</v>
+        <v>802800</v>
       </c>
       <c r="I61" s="3">
-        <v>781100</v>
+        <v>773900</v>
       </c>
       <c r="J61" s="3">
-        <v>736600</v>
+        <v>729800</v>
       </c>
       <c r="K61" s="3">
         <v>815400</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>344200</v>
+        <v>341100</v>
       </c>
       <c r="E62" s="3">
-        <v>420100</v>
+        <v>416300</v>
       </c>
       <c r="F62" s="3">
-        <v>298700</v>
+        <v>296000</v>
       </c>
       <c r="G62" s="3">
-        <v>327200</v>
+        <v>324200</v>
       </c>
       <c r="H62" s="3">
-        <v>291100</v>
+        <v>288400</v>
       </c>
       <c r="I62" s="3">
-        <v>233700</v>
+        <v>231500</v>
       </c>
       <c r="J62" s="3">
-        <v>215400</v>
+        <v>213400</v>
       </c>
       <c r="K62" s="3">
         <v>243900</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2218400</v>
+        <v>2198000</v>
       </c>
       <c r="E66" s="3">
-        <v>2349400</v>
+        <v>2327900</v>
       </c>
       <c r="F66" s="3">
-        <v>2038300</v>
+        <v>2019600</v>
       </c>
       <c r="G66" s="3">
-        <v>1784200</v>
+        <v>1767800</v>
       </c>
       <c r="H66" s="3">
-        <v>1572100</v>
+        <v>1557700</v>
       </c>
       <c r="I66" s="3">
-        <v>1494100</v>
+        <v>1480300</v>
       </c>
       <c r="J66" s="3">
-        <v>1442700</v>
+        <v>1429400</v>
       </c>
       <c r="K66" s="3">
         <v>1557700</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1310700</v>
+        <v>1298700</v>
       </c>
       <c r="E72" s="3">
-        <v>1253600</v>
+        <v>1242100</v>
       </c>
       <c r="F72" s="3">
-        <v>1309400</v>
+        <v>1297400</v>
       </c>
       <c r="G72" s="3">
-        <v>1185200</v>
+        <v>1174300</v>
       </c>
       <c r="H72" s="3">
-        <v>1127100</v>
+        <v>1116800</v>
       </c>
       <c r="I72" s="3">
-        <v>976000</v>
+        <v>967000</v>
       </c>
       <c r="J72" s="3">
-        <v>831300</v>
+        <v>823700</v>
       </c>
       <c r="K72" s="3">
         <v>816800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>966100</v>
+        <v>957200</v>
       </c>
       <c r="E76" s="3">
-        <v>932200</v>
+        <v>923700</v>
       </c>
       <c r="F76" s="3">
-        <v>1173000</v>
+        <v>1162200</v>
       </c>
       <c r="G76" s="3">
-        <v>884200</v>
+        <v>876100</v>
       </c>
       <c r="H76" s="3">
-        <v>1034000</v>
+        <v>1024500</v>
       </c>
       <c r="I76" s="3">
-        <v>919800</v>
+        <v>911300</v>
       </c>
       <c r="J76" s="3">
-        <v>862500</v>
+        <v>854600</v>
       </c>
       <c r="K76" s="3">
         <v>927300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>186900</v>
+        <v>185200</v>
       </c>
       <c r="E81" s="3">
-        <v>136800</v>
+        <v>135500</v>
       </c>
       <c r="F81" s="3">
-        <v>168600</v>
+        <v>167100</v>
       </c>
       <c r="G81" s="3">
-        <v>133000</v>
+        <v>131800</v>
       </c>
       <c r="H81" s="3">
-        <v>189400</v>
+        <v>187600</v>
       </c>
       <c r="I81" s="3">
-        <v>105300</v>
+        <v>104300</v>
       </c>
       <c r="J81" s="3">
-        <v>128400</v>
+        <v>127300</v>
       </c>
       <c r="K81" s="3">
         <v>102300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>384600</v>
+        <v>381100</v>
       </c>
       <c r="E89" s="3">
-        <v>415100</v>
+        <v>411300</v>
       </c>
       <c r="F89" s="3">
-        <v>325700</v>
+        <v>322800</v>
       </c>
       <c r="G89" s="3">
-        <v>301200</v>
+        <v>298500</v>
       </c>
       <c r="H89" s="3">
-        <v>275900</v>
+        <v>273400</v>
       </c>
       <c r="I89" s="3">
-        <v>251200</v>
+        <v>248900</v>
       </c>
       <c r="J89" s="3">
-        <v>270300</v>
+        <v>267800</v>
       </c>
       <c r="K89" s="3">
         <v>252500</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-210100</v>
+        <v>-208100</v>
       </c>
       <c r="E91" s="3">
-        <v>-203500</v>
+        <v>-201600</v>
       </c>
       <c r="F91" s="3">
-        <v>-151400</v>
+        <v>-150000</v>
       </c>
       <c r="G91" s="3">
-        <v>-93600</v>
+        <v>-92700</v>
       </c>
       <c r="H91" s="3">
-        <v>-120600</v>
+        <v>-119500</v>
       </c>
       <c r="I91" s="3">
-        <v>-132000</v>
+        <v>-130700</v>
       </c>
       <c r="J91" s="3">
-        <v>-184100</v>
+        <v>-182400</v>
       </c>
       <c r="K91" s="3">
         <v>-144900</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-172500</v>
+        <v>-171000</v>
       </c>
       <c r="E94" s="3">
-        <v>-92800</v>
+        <v>-92000</v>
       </c>
       <c r="F94" s="3">
-        <v>-216100</v>
+        <v>-214100</v>
       </c>
       <c r="G94" s="3">
-        <v>-244000</v>
+        <v>-241800</v>
       </c>
       <c r="H94" s="3">
-        <v>-120000</v>
+        <v>-118900</v>
       </c>
       <c r="I94" s="3">
-        <v>-128700</v>
+        <v>-127500</v>
       </c>
       <c r="J94" s="3">
-        <v>-184000</v>
+        <v>-182300</v>
       </c>
       <c r="K94" s="3">
         <v>-128700</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-180800</v>
+        <v>-179100</v>
       </c>
       <c r="E96" s="3">
-        <v>-299000</v>
+        <v>-296300</v>
       </c>
       <c r="F96" s="3">
-        <v>-115900</v>
+        <v>-114900</v>
       </c>
       <c r="G96" s="3">
-        <v>-109000</v>
+        <v>-108000</v>
       </c>
       <c r="H96" s="3">
-        <v>-94000</v>
+        <v>-93200</v>
       </c>
       <c r="I96" s="3">
-        <v>-95400</v>
+        <v>-94500</v>
       </c>
       <c r="J96" s="3">
-        <v>-81700</v>
+        <v>-81000</v>
       </c>
       <c r="K96" s="3">
         <v>-76400</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-204000</v>
+        <v>-202100</v>
       </c>
       <c r="E100" s="3">
-        <v>-312800</v>
+        <v>-309900</v>
       </c>
       <c r="F100" s="3">
-        <v>-125700</v>
+        <v>-124500</v>
       </c>
       <c r="G100" s="3">
-        <v>123200</v>
+        <v>122100</v>
       </c>
       <c r="H100" s="3">
-        <v>-138600</v>
+        <v>-137300</v>
       </c>
       <c r="I100" s="3">
-        <v>-125000</v>
+        <v>-123800</v>
       </c>
       <c r="J100" s="3">
-        <v>-85400</v>
+        <v>-84600</v>
       </c>
       <c r="K100" s="3">
         <v>-111000</v>
@@ -4452,16 +4452,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="E101" s="3">
-        <v>-23300</v>
+        <v>-23100</v>
       </c>
       <c r="F101" s="3">
-        <v>10400</v>
+        <v>10300</v>
       </c>
       <c r="G101" s="3">
-        <v>-14800</v>
+        <v>-14700</v>
       </c>
       <c r="H101" s="3">
         <v>4400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>13100</v>
+        <v>13000</v>
       </c>
       <c r="E102" s="3">
-        <v>-13800</v>
+        <v>-13600</v>
       </c>
       <c r="F102" s="3">
-        <v>-5700</v>
+        <v>-5600</v>
       </c>
       <c r="G102" s="3">
-        <v>165600</v>
+        <v>164100</v>
       </c>
       <c r="H102" s="3">
-        <v>21800</v>
+        <v>21600</v>
       </c>
       <c r="I102" s="3">
         <v>1400</v>
       </c>
       <c r="J102" s="3">
-        <v>-5500</v>
+        <v>-5400</v>
       </c>
       <c r="K102" s="3">
         <v>13700</v>

--- a/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2827900</v>
+        <v>2986700</v>
       </c>
       <c r="E8" s="3">
-        <v>2869400</v>
+        <v>3127400</v>
       </c>
       <c r="F8" s="3">
-        <v>2394100</v>
+        <v>2601800</v>
       </c>
       <c r="G8" s="3">
-        <v>1834100</v>
+        <v>2390300</v>
       </c>
       <c r="H8" s="3">
-        <v>1921300</v>
+        <v>2366000</v>
       </c>
       <c r="I8" s="3">
-        <v>1806700</v>
+        <v>2410800</v>
       </c>
       <c r="J8" s="3">
-        <v>1996800</v>
+        <v>3004000</v>
       </c>
       <c r="K8" s="3">
         <v>2008500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1730200</v>
+        <v>1827300</v>
       </c>
       <c r="E9" s="3">
-        <v>1759000</v>
+        <v>1917100</v>
       </c>
       <c r="F9" s="3">
-        <v>1485400</v>
+        <v>1614300</v>
       </c>
       <c r="G9" s="3">
-        <v>1104300</v>
+        <v>1439100</v>
       </c>
       <c r="H9" s="3">
-        <v>1132200</v>
+        <v>1394200</v>
       </c>
       <c r="I9" s="3">
-        <v>1045500</v>
+        <v>1395000</v>
       </c>
       <c r="J9" s="3">
-        <v>1154500</v>
+        <v>1736900</v>
       </c>
       <c r="K9" s="3">
         <v>1168300</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1097800</v>
+        <v>1159400</v>
       </c>
       <c r="E10" s="3">
-        <v>1110400</v>
+        <v>1210300</v>
       </c>
       <c r="F10" s="3">
-        <v>908600</v>
+        <v>987500</v>
       </c>
       <c r="G10" s="3">
-        <v>729800</v>
+        <v>951100</v>
       </c>
       <c r="H10" s="3">
-        <v>789100</v>
+        <v>971800</v>
       </c>
       <c r="I10" s="3">
-        <v>761300</v>
+        <v>1015800</v>
       </c>
       <c r="J10" s="3">
-        <v>842200</v>
+        <v>1267100</v>
       </c>
       <c r="K10" s="3">
         <v>840200</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>28800</v>
+        <v>8300</v>
       </c>
       <c r="E14" s="3">
-        <v>25000</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="3">
-        <v>500</v>
+        <v>-100</v>
       </c>
       <c r="G14" s="3">
-        <v>8600</v>
+        <v>11200</v>
       </c>
       <c r="H14" s="3">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="I14" s="3">
-        <v>300</v>
+        <v>-2500</v>
       </c>
       <c r="J14" s="3">
-        <v>3300</v>
+        <v>4400</v>
       </c>
       <c r="K14" s="3">
         <v>5400</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>110500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>123800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>142100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>133700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>140700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>158300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2486300</v>
+        <v>2600000</v>
       </c>
       <c r="E17" s="3">
-        <v>2521900</v>
+        <v>2722200</v>
       </c>
       <c r="F17" s="3">
-        <v>2093200</v>
+        <v>2275900</v>
       </c>
       <c r="G17" s="3">
-        <v>1585200</v>
+        <v>2066300</v>
       </c>
       <c r="H17" s="3">
-        <v>1648600</v>
+        <v>2080600</v>
       </c>
       <c r="I17" s="3">
-        <v>1580800</v>
+        <v>2108800</v>
       </c>
       <c r="J17" s="3">
-        <v>1759100</v>
+        <v>2638300</v>
       </c>
       <c r="K17" s="3">
         <v>1794600</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>341600</v>
+        <v>386600</v>
       </c>
       <c r="E18" s="3">
-        <v>347500</v>
+        <v>405200</v>
       </c>
       <c r="F18" s="3">
-        <v>300800</v>
+        <v>325900</v>
       </c>
       <c r="G18" s="3">
-        <v>249000</v>
+        <v>323900</v>
       </c>
       <c r="H18" s="3">
-        <v>272800</v>
+        <v>285400</v>
       </c>
       <c r="I18" s="3">
-        <v>226000</v>
+        <v>302000</v>
       </c>
       <c r="J18" s="3">
-        <v>237600</v>
+        <v>365700</v>
       </c>
       <c r="K18" s="3">
         <v>213900</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4800</v>
+        <v>41800</v>
       </c>
       <c r="E20" s="3">
-        <v>-35900</v>
+        <v>103800</v>
       </c>
       <c r="F20" s="3">
-        <v>-26600</v>
+        <v>30500</v>
       </c>
       <c r="G20" s="3">
-        <v>-5800</v>
+        <v>4400</v>
       </c>
       <c r="H20" s="3">
-        <v>25200</v>
+        <v>-80800</v>
       </c>
       <c r="I20" s="3">
-        <v>-17100</v>
+        <v>27300</v>
       </c>
       <c r="J20" s="3">
-        <v>-1600</v>
+        <v>19800</v>
       </c>
       <c r="K20" s="3">
         <v>-3100</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>346400</v>
+        <v>455400</v>
       </c>
       <c r="E21" s="3">
-        <v>311600</v>
+        <v>425200</v>
       </c>
       <c r="F21" s="3">
-        <v>274200</v>
+        <v>405400</v>
       </c>
       <c r="G21" s="3">
-        <v>243100</v>
+        <v>461700</v>
       </c>
       <c r="H21" s="3">
-        <v>298000</v>
+        <v>499900</v>
       </c>
       <c r="I21" s="3">
-        <v>208900</v>
+        <v>415400</v>
       </c>
       <c r="J21" s="3">
-        <v>236000</v>
+        <v>504200</v>
       </c>
       <c r="K21" s="3">
         <v>210700</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>65100</v>
+        <v>68800</v>
       </c>
       <c r="E22" s="3">
-        <v>60200</v>
+        <v>65600</v>
       </c>
       <c r="F22" s="3">
-        <v>54800</v>
+        <v>59500</v>
       </c>
       <c r="G22" s="3">
-        <v>50900</v>
+        <v>68900</v>
       </c>
       <c r="H22" s="3">
-        <v>42600</v>
+        <v>52500</v>
       </c>
       <c r="I22" s="3">
-        <v>43600</v>
+        <v>58200</v>
       </c>
       <c r="J22" s="3">
-        <v>51600</v>
+        <v>77600</v>
       </c>
       <c r="K22" s="3">
         <v>51600</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>281300</v>
+        <v>297100</v>
       </c>
       <c r="E23" s="3">
-        <v>251400</v>
+        <v>274000</v>
       </c>
       <c r="F23" s="3">
-        <v>219500</v>
+        <v>238500</v>
       </c>
       <c r="G23" s="3">
-        <v>192300</v>
+        <v>250600</v>
       </c>
       <c r="H23" s="3">
-        <v>255300</v>
+        <v>314400</v>
       </c>
       <c r="I23" s="3">
-        <v>165300</v>
+        <v>220500</v>
       </c>
       <c r="J23" s="3">
-        <v>184500</v>
+        <v>277500</v>
       </c>
       <c r="K23" s="3">
         <v>159200</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>92900</v>
+        <v>98100</v>
       </c>
       <c r="E24" s="3">
-        <v>112700</v>
+        <v>122800</v>
       </c>
       <c r="F24" s="3">
-        <v>49900</v>
+        <v>54200</v>
       </c>
       <c r="G24" s="3">
-        <v>59300</v>
+        <v>77300</v>
       </c>
       <c r="H24" s="3">
-        <v>66100</v>
+        <v>81300</v>
       </c>
       <c r="I24" s="3">
-        <v>60000</v>
+        <v>80100</v>
       </c>
       <c r="J24" s="3">
-        <v>55900</v>
+        <v>84200</v>
       </c>
       <c r="K24" s="3">
         <v>55200</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>188500</v>
+        <v>199100</v>
       </c>
       <c r="E26" s="3">
-        <v>138700</v>
+        <v>151200</v>
       </c>
       <c r="F26" s="3">
-        <v>169600</v>
+        <v>184300</v>
       </c>
       <c r="G26" s="3">
-        <v>133000</v>
+        <v>173300</v>
       </c>
       <c r="H26" s="3">
-        <v>189300</v>
+        <v>233100</v>
       </c>
       <c r="I26" s="3">
-        <v>105200</v>
+        <v>140400</v>
       </c>
       <c r="J26" s="3">
-        <v>128500</v>
+        <v>193300</v>
       </c>
       <c r="K26" s="3">
         <v>104000</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>185200</v>
+        <v>195600</v>
       </c>
       <c r="E27" s="3">
-        <v>135500</v>
+        <v>147700</v>
       </c>
       <c r="F27" s="3">
-        <v>167100</v>
+        <v>181600</v>
       </c>
       <c r="G27" s="3">
-        <v>131800</v>
+        <v>171700</v>
       </c>
       <c r="H27" s="3">
-        <v>187600</v>
+        <v>231000</v>
       </c>
       <c r="I27" s="3">
-        <v>104300</v>
+        <v>139200</v>
       </c>
       <c r="J27" s="3">
-        <v>127300</v>
+        <v>191500</v>
       </c>
       <c r="K27" s="3">
         <v>102300</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4800</v>
+        <v>-41800</v>
       </c>
       <c r="E32" s="3">
-        <v>35900</v>
+        <v>-103800</v>
       </c>
       <c r="F32" s="3">
-        <v>26600</v>
+        <v>-30500</v>
       </c>
       <c r="G32" s="3">
-        <v>5800</v>
+        <v>-4400</v>
       </c>
       <c r="H32" s="3">
-        <v>-25200</v>
+        <v>80800</v>
       </c>
       <c r="I32" s="3">
-        <v>17100</v>
+        <v>-27300</v>
       </c>
       <c r="J32" s="3">
-        <v>1600</v>
+        <v>-19800</v>
       </c>
       <c r="K32" s="3">
         <v>3100</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>185200</v>
+        <v>195600</v>
       </c>
       <c r="E33" s="3">
-        <v>135500</v>
+        <v>147700</v>
       </c>
       <c r="F33" s="3">
-        <v>167100</v>
+        <v>181600</v>
       </c>
       <c r="G33" s="3">
-        <v>131800</v>
+        <v>171700</v>
       </c>
       <c r="H33" s="3">
-        <v>187600</v>
+        <v>231000</v>
       </c>
       <c r="I33" s="3">
-        <v>104300</v>
+        <v>139200</v>
       </c>
       <c r="J33" s="3">
-        <v>127300</v>
+        <v>191500</v>
       </c>
       <c r="K33" s="3">
         <v>102300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>185200</v>
+        <v>195600</v>
       </c>
       <c r="E35" s="3">
-        <v>135500</v>
+        <v>147700</v>
       </c>
       <c r="F35" s="3">
-        <v>167100</v>
+        <v>181600</v>
       </c>
       <c r="G35" s="3">
-        <v>131800</v>
+        <v>171700</v>
       </c>
       <c r="H35" s="3">
-        <v>187600</v>
+        <v>231000</v>
       </c>
       <c r="I35" s="3">
-        <v>104300</v>
+        <v>139200</v>
       </c>
       <c r="J35" s="3">
-        <v>127300</v>
+        <v>191500</v>
       </c>
       <c r="K35" s="3">
         <v>102300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>129500</v>
+        <v>346400</v>
       </c>
       <c r="E41" s="3">
-        <v>117400</v>
+        <v>343300</v>
       </c>
       <c r="F41" s="3">
-        <v>102600</v>
+        <v>357200</v>
       </c>
       <c r="G41" s="3">
-        <v>90000</v>
+        <v>435700</v>
       </c>
       <c r="H41" s="3">
-        <v>57800</v>
+        <v>209600</v>
       </c>
       <c r="I41" s="3">
-        <v>54900</v>
+        <v>198200</v>
       </c>
       <c r="J41" s="3">
-        <v>43200</v>
+        <v>221400</v>
       </c>
       <c r="K41" s="3">
         <v>31500</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>270000</v>
+        <v>75500</v>
       </c>
       <c r="E42" s="3">
-        <v>297900</v>
+        <v>109300</v>
       </c>
       <c r="F42" s="3">
-        <v>436200</v>
+        <v>228300</v>
       </c>
       <c r="G42" s="3">
-        <v>395800</v>
+        <v>197500</v>
       </c>
       <c r="H42" s="3">
-        <v>112400</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>93700</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>118700</v>
+        <v>22200</v>
       </c>
       <c r="K42" s="3">
         <v>190800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>388100</v>
+        <v>409900</v>
       </c>
       <c r="E43" s="3">
-        <v>361900</v>
+        <v>394400</v>
       </c>
       <c r="F43" s="3">
-        <v>310100</v>
+        <v>337000</v>
       </c>
       <c r="G43" s="3">
-        <v>222900</v>
+        <v>290400</v>
       </c>
       <c r="H43" s="3">
-        <v>228900</v>
+        <v>281800</v>
       </c>
       <c r="I43" s="3">
-        <v>191600</v>
+        <v>268200</v>
       </c>
       <c r="J43" s="3">
-        <v>203900</v>
+        <v>306700</v>
       </c>
       <c r="K43" s="3">
         <v>213800</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>251700</v>
+        <v>265800</v>
       </c>
       <c r="E44" s="3">
-        <v>265600</v>
+        <v>289400</v>
       </c>
       <c r="F44" s="3">
-        <v>206700</v>
+        <v>224600</v>
       </c>
       <c r="G44" s="3">
-        <v>138200</v>
+        <v>180100</v>
       </c>
       <c r="H44" s="3">
-        <v>159500</v>
+        <v>196400</v>
       </c>
       <c r="I44" s="3">
-        <v>163400</v>
+        <v>218100</v>
       </c>
       <c r="J44" s="3">
-        <v>141900</v>
+        <v>213400</v>
       </c>
       <c r="K44" s="3">
         <v>163500</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>21000</v>
+        <v>9200</v>
       </c>
       <c r="E45" s="3">
-        <v>212000</v>
+        <v>223900</v>
       </c>
       <c r="F45" s="3">
-        <v>14800</v>
+        <v>6800</v>
       </c>
       <c r="G45" s="3">
-        <v>14200</v>
+        <v>7300</v>
       </c>
       <c r="H45" s="3">
-        <v>17600</v>
+        <v>6800</v>
       </c>
       <c r="I45" s="3">
-        <v>16500</v>
+        <v>2400</v>
       </c>
       <c r="J45" s="3">
-        <v>15100</v>
+        <v>1700</v>
       </c>
       <c r="K45" s="3">
         <v>24900</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1060300</v>
+        <v>1119800</v>
       </c>
       <c r="E46" s="3">
-        <v>1254700</v>
+        <v>1367500</v>
       </c>
       <c r="F46" s="3">
-        <v>1070300</v>
+        <v>1163100</v>
       </c>
       <c r="G46" s="3">
-        <v>861100</v>
+        <v>1122200</v>
       </c>
       <c r="H46" s="3">
-        <v>576200</v>
+        <v>709500</v>
       </c>
       <c r="I46" s="3">
-        <v>520100</v>
+        <v>694000</v>
       </c>
       <c r="J46" s="3">
-        <v>522700</v>
+        <v>786400</v>
       </c>
       <c r="K46" s="3">
         <v>624600</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>157700</v>
+        <v>121100</v>
       </c>
       <c r="E47" s="3">
-        <v>165700</v>
+        <v>131700</v>
       </c>
       <c r="F47" s="3">
-        <v>157300</v>
+        <v>125300</v>
       </c>
       <c r="G47" s="3">
-        <v>178900</v>
+        <v>139300</v>
       </c>
       <c r="H47" s="3">
-        <v>221900</v>
+        <v>148600</v>
       </c>
       <c r="I47" s="3">
-        <v>126400</v>
+        <v>161900</v>
       </c>
       <c r="J47" s="3">
-        <v>99000</v>
+        <v>161100</v>
       </c>
       <c r="K47" s="3">
         <v>94700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>942200</v>
+        <v>995100</v>
       </c>
       <c r="E48" s="3">
-        <v>862100</v>
+        <v>939600</v>
       </c>
       <c r="F48" s="3">
-        <v>773700</v>
+        <v>840800</v>
       </c>
       <c r="G48" s="3">
-        <v>654000</v>
+        <v>852300</v>
       </c>
       <c r="H48" s="3">
-        <v>780500</v>
+        <v>961200</v>
       </c>
       <c r="I48" s="3">
-        <v>767600</v>
+        <v>1024300</v>
       </c>
       <c r="J48" s="3">
-        <v>712500</v>
+        <v>1071900</v>
       </c>
       <c r="K48" s="3">
         <v>752800</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>883500</v>
+        <v>933100</v>
       </c>
       <c r="E49" s="3">
-        <v>864900</v>
+        <v>942600</v>
       </c>
       <c r="F49" s="3">
-        <v>839900</v>
+        <v>912800</v>
       </c>
       <c r="G49" s="3">
-        <v>759100</v>
+        <v>989200</v>
       </c>
       <c r="H49" s="3">
-        <v>860000</v>
+        <v>1059000</v>
       </c>
       <c r="I49" s="3">
-        <v>848900</v>
+        <v>1132800</v>
       </c>
       <c r="J49" s="3">
-        <v>817400</v>
+        <v>1229700</v>
       </c>
       <c r="K49" s="3">
         <v>885800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>111600</v>
+        <v>158200</v>
       </c>
       <c r="E52" s="3">
-        <v>104200</v>
+        <v>159400</v>
       </c>
       <c r="F52" s="3">
-        <v>340600</v>
+        <v>413500</v>
       </c>
       <c r="G52" s="3">
-        <v>190800</v>
+        <v>339600</v>
       </c>
       <c r="H52" s="3">
-        <v>143700</v>
+        <v>299300</v>
       </c>
       <c r="I52" s="3">
-        <v>128500</v>
+        <v>178200</v>
       </c>
       <c r="J52" s="3">
-        <v>132400</v>
+        <v>181400</v>
       </c>
       <c r="K52" s="3">
         <v>127100</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3155200</v>
+        <v>3332400</v>
       </c>
       <c r="E54" s="3">
-        <v>3251600</v>
+        <v>3543900</v>
       </c>
       <c r="F54" s="3">
-        <v>3181800</v>
+        <v>3457900</v>
       </c>
       <c r="G54" s="3">
-        <v>2643900</v>
+        <v>3445600</v>
       </c>
       <c r="H54" s="3">
-        <v>2582200</v>
+        <v>3179800</v>
       </c>
       <c r="I54" s="3">
-        <v>2391700</v>
+        <v>3191300</v>
       </c>
       <c r="J54" s="3">
-        <v>2284000</v>
+        <v>3436100</v>
       </c>
       <c r="K54" s="3">
         <v>2485000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>567000</v>
+        <v>598200</v>
       </c>
       <c r="E57" s="3">
-        <v>513100</v>
+        <v>558500</v>
       </c>
       <c r="F57" s="3">
-        <v>414200</v>
+        <v>449700</v>
       </c>
       <c r="G57" s="3">
-        <v>291600</v>
+        <v>379800</v>
       </c>
       <c r="H57" s="3">
-        <v>321100</v>
+        <v>395400</v>
       </c>
       <c r="I57" s="3">
-        <v>306700</v>
+        <v>409200</v>
       </c>
       <c r="J57" s="3">
-        <v>314800</v>
+        <v>473500</v>
       </c>
       <c r="K57" s="3">
         <v>324300</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>42000</v>
+        <v>44400</v>
       </c>
       <c r="E58" s="3">
-        <v>376400</v>
+        <v>410300</v>
       </c>
       <c r="F58" s="3">
-        <v>36300</v>
+        <v>39400</v>
       </c>
       <c r="G58" s="3">
-        <v>27200</v>
+        <v>35500</v>
       </c>
       <c r="H58" s="3">
-        <v>31400</v>
+        <v>38600</v>
       </c>
       <c r="I58" s="3">
-        <v>47200</v>
+        <v>63000</v>
       </c>
       <c r="J58" s="3">
-        <v>58000</v>
+        <v>87200</v>
       </c>
       <c r="K58" s="3">
         <v>56600</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>139300</v>
+        <v>81700</v>
       </c>
       <c r="E59" s="3">
-        <v>135700</v>
+        <v>91600</v>
       </c>
       <c r="F59" s="3">
-        <v>121400</v>
+        <v>91300</v>
       </c>
       <c r="G59" s="3">
-        <v>89500</v>
+        <v>73000</v>
       </c>
       <c r="H59" s="3">
-        <v>92100</v>
+        <v>62300</v>
       </c>
       <c r="I59" s="3">
-        <v>99600</v>
+        <v>85000</v>
       </c>
       <c r="J59" s="3">
-        <v>89800</v>
+        <v>76600</v>
       </c>
       <c r="K59" s="3">
         <v>93200</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>748300</v>
+        <v>790300</v>
       </c>
       <c r="E60" s="3">
-        <v>1025200</v>
+        <v>1117400</v>
       </c>
       <c r="F60" s="3">
-        <v>571900</v>
+        <v>621600</v>
       </c>
       <c r="G60" s="3">
-        <v>408300</v>
+        <v>532100</v>
       </c>
       <c r="H60" s="3">
-        <v>444600</v>
+        <v>547500</v>
       </c>
       <c r="I60" s="3">
-        <v>453500</v>
+        <v>605100</v>
       </c>
       <c r="J60" s="3">
-        <v>462600</v>
+        <v>695900</v>
       </c>
       <c r="K60" s="3">
         <v>474100</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1071200</v>
+        <v>1131400</v>
       </c>
       <c r="E61" s="3">
-        <v>856000</v>
+        <v>933000</v>
       </c>
       <c r="F61" s="3">
-        <v>1124300</v>
+        <v>1221900</v>
       </c>
       <c r="G61" s="3">
-        <v>1013300</v>
+        <v>1320600</v>
       </c>
       <c r="H61" s="3">
-        <v>802800</v>
+        <v>988600</v>
       </c>
       <c r="I61" s="3">
-        <v>773900</v>
+        <v>1032600</v>
       </c>
       <c r="J61" s="3">
-        <v>729800</v>
+        <v>1098000</v>
       </c>
       <c r="K61" s="3">
         <v>815400</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>341100</v>
+        <v>133300</v>
       </c>
       <c r="E62" s="3">
-        <v>416300</v>
+        <v>238100</v>
       </c>
       <c r="F62" s="3">
-        <v>296000</v>
+        <v>107400</v>
       </c>
       <c r="G62" s="3">
-        <v>324200</v>
+        <v>187000</v>
       </c>
       <c r="H62" s="3">
-        <v>288400</v>
+        <v>116300</v>
       </c>
       <c r="I62" s="3">
-        <v>231500</v>
+        <v>86000</v>
       </c>
       <c r="J62" s="3">
-        <v>213400</v>
+        <v>104100</v>
       </c>
       <c r="K62" s="3">
         <v>243900</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2198000</v>
+        <v>2281900</v>
       </c>
       <c r="E66" s="3">
-        <v>2327900</v>
+        <v>2504000</v>
       </c>
       <c r="F66" s="3">
-        <v>2019600</v>
+        <v>2165100</v>
       </c>
       <c r="G66" s="3">
-        <v>1767800</v>
+        <v>2275200</v>
       </c>
       <c r="H66" s="3">
-        <v>1557700</v>
+        <v>1891200</v>
       </c>
       <c r="I66" s="3">
-        <v>1480300</v>
+        <v>1946600</v>
       </c>
       <c r="J66" s="3">
-        <v>1429400</v>
+        <v>2114800</v>
       </c>
       <c r="K66" s="3">
         <v>1557700</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1298700</v>
+        <v>883700</v>
       </c>
       <c r="E72" s="3">
-        <v>1242100</v>
+        <v>850300</v>
       </c>
       <c r="F72" s="3">
-        <v>1297400</v>
+        <v>907900</v>
       </c>
       <c r="G72" s="3">
-        <v>1174300</v>
+        <v>928400</v>
       </c>
       <c r="H72" s="3">
-        <v>1116800</v>
+        <v>799200</v>
       </c>
       <c r="I72" s="3">
-        <v>967000</v>
+        <v>666100</v>
       </c>
       <c r="J72" s="3">
-        <v>823700</v>
+        <v>554000</v>
       </c>
       <c r="K72" s="3">
         <v>816800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>957200</v>
+        <v>1010900</v>
       </c>
       <c r="E76" s="3">
-        <v>923700</v>
+        <v>1006700</v>
       </c>
       <c r="F76" s="3">
-        <v>1162200</v>
+        <v>1263100</v>
       </c>
       <c r="G76" s="3">
-        <v>876100</v>
+        <v>1141700</v>
       </c>
       <c r="H76" s="3">
-        <v>1024500</v>
+        <v>1261600</v>
       </c>
       <c r="I76" s="3">
-        <v>911300</v>
+        <v>1216000</v>
       </c>
       <c r="J76" s="3">
-        <v>854600</v>
+        <v>1285700</v>
       </c>
       <c r="K76" s="3">
         <v>927300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>185200</v>
+        <v>195600</v>
       </c>
       <c r="E81" s="3">
-        <v>135500</v>
+        <v>147700</v>
       </c>
       <c r="F81" s="3">
-        <v>167100</v>
+        <v>181600</v>
       </c>
       <c r="G81" s="3">
-        <v>131800</v>
+        <v>171700</v>
       </c>
       <c r="H81" s="3">
-        <v>187600</v>
+        <v>231000</v>
       </c>
       <c r="I81" s="3">
-        <v>104300</v>
+        <v>139200</v>
       </c>
       <c r="J81" s="3">
-        <v>127300</v>
+        <v>191500</v>
       </c>
       <c r="K81" s="3">
         <v>102300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>122900</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>135300</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>119700</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>144500</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>140500</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>158100</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>381100</v>
+        <v>418400</v>
       </c>
       <c r="E89" s="3">
-        <v>411300</v>
+        <v>467800</v>
       </c>
       <c r="F89" s="3">
-        <v>322800</v>
+        <v>358000</v>
       </c>
       <c r="G89" s="3">
-        <v>298500</v>
+        <v>392400</v>
       </c>
       <c r="H89" s="3">
-        <v>273400</v>
+        <v>339300</v>
       </c>
       <c r="I89" s="3">
-        <v>248900</v>
+        <v>339100</v>
       </c>
       <c r="J89" s="3">
-        <v>267800</v>
+        <v>402900</v>
       </c>
       <c r="K89" s="3">
         <v>252500</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-208100</v>
+        <v>-219800</v>
       </c>
       <c r="E91" s="3">
-        <v>-201600</v>
+        <v>-219800</v>
       </c>
       <c r="F91" s="3">
-        <v>-150000</v>
+        <v>-163000</v>
       </c>
       <c r="G91" s="3">
-        <v>-92700</v>
+        <v>-120900</v>
       </c>
       <c r="H91" s="3">
-        <v>-119500</v>
+        <v>-147200</v>
       </c>
       <c r="I91" s="3">
-        <v>-130700</v>
+        <v>-174500</v>
       </c>
       <c r="J91" s="3">
-        <v>-182400</v>
+        <v>-274400</v>
       </c>
       <c r="K91" s="3">
         <v>-144900</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-171000</v>
+        <v>-180500</v>
       </c>
       <c r="E94" s="3">
-        <v>-92000</v>
+        <v>-100300</v>
       </c>
       <c r="F94" s="3">
-        <v>-214100</v>
+        <v>-232700</v>
       </c>
       <c r="G94" s="3">
-        <v>-241800</v>
+        <v>-315100</v>
       </c>
       <c r="H94" s="3">
-        <v>-118900</v>
+        <v>-146400</v>
       </c>
       <c r="I94" s="3">
-        <v>-127500</v>
+        <v>-170200</v>
       </c>
       <c r="J94" s="3">
-        <v>-182300</v>
+        <v>-274300</v>
       </c>
       <c r="K94" s="3">
         <v>-128700</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-179100</v>
+        <v>189200</v>
       </c>
       <c r="E96" s="3">
-        <v>-296300</v>
+        <v>322900</v>
       </c>
       <c r="F96" s="3">
-        <v>-114900</v>
+        <v>124800</v>
       </c>
       <c r="G96" s="3">
-        <v>-108000</v>
+        <v>140700</v>
       </c>
       <c r="H96" s="3">
-        <v>-93200</v>
+        <v>114700</v>
       </c>
       <c r="I96" s="3">
-        <v>-94500</v>
+        <v>126100</v>
       </c>
       <c r="J96" s="3">
-        <v>-81000</v>
+        <v>121800</v>
       </c>
       <c r="K96" s="3">
         <v>-76400</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-202100</v>
+        <v>-213400</v>
       </c>
       <c r="E100" s="3">
-        <v>-309900</v>
+        <v>-337800</v>
       </c>
       <c r="F100" s="3">
-        <v>-124500</v>
+        <v>-135400</v>
       </c>
       <c r="G100" s="3">
-        <v>122100</v>
+        <v>159100</v>
       </c>
       <c r="H100" s="3">
-        <v>-137300</v>
+        <v>-169100</v>
       </c>
       <c r="I100" s="3">
-        <v>-123800</v>
+        <v>-165200</v>
       </c>
       <c r="J100" s="3">
-        <v>-84600</v>
+        <v>-127300</v>
       </c>
       <c r="K100" s="3">
         <v>-111000</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>4900</v>
+        <v>5200</v>
       </c>
       <c r="E101" s="3">
-        <v>-23100</v>
+        <v>-25100</v>
       </c>
       <c r="F101" s="3">
-        <v>10300</v>
+        <v>11200</v>
       </c>
       <c r="G101" s="3">
-        <v>-14700</v>
+        <v>-19100</v>
       </c>
       <c r="H101" s="3">
-        <v>4400</v>
+        <v>5400</v>
       </c>
       <c r="I101" s="3">
-        <v>3900</v>
+        <v>5200</v>
       </c>
       <c r="J101" s="3">
-        <v>-6300</v>
+        <v>-9400</v>
       </c>
       <c r="K101" s="3">
         <v>900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>13000</v>
+        <v>29600</v>
       </c>
       <c r="E102" s="3">
-        <v>-13600</v>
+        <v>4700</v>
       </c>
       <c r="F102" s="3">
-        <v>-5600</v>
+        <v>1200</v>
       </c>
       <c r="G102" s="3">
-        <v>164100</v>
+        <v>217300</v>
       </c>
       <c r="H102" s="3">
-        <v>21600</v>
+        <v>29300</v>
       </c>
       <c r="I102" s="3">
-        <v>1400</v>
+        <v>8800</v>
       </c>
       <c r="J102" s="3">
-        <v>-5400</v>
+        <v>-8200</v>
       </c>
       <c r="K102" s="3">
         <v>13700</v>

--- a/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>AKO.B</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3244600</v>
+      </c>
+      <c r="E8" s="3">
         <v>2986700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3127400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2601800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2390300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2366000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2410800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3004000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2008500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2102700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2138700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1978200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1500500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1484100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1957700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1827300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1917100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1614300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1439100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1394200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1395000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1736900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1168300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1239500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1286700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1189300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>894700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>873700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1287000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1159400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1210300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>987500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>951100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>971800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1015800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1267100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>840200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>863200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>852000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>788900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>605900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>610500</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,81 +979,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>8300</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-100</v>
       </c>
       <c r="F14" s="3">
         <v>-100</v>
       </c>
       <c r="G14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H14" s="3">
         <v>11200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3700</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>122100</v>
+      </c>
+      <c r="E15" s="3">
         <v>110500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>123800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>110000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>142100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>133700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>140700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>158300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2814800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2722200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2275900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2066300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2080600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2108800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2638300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1794600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1892400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1935700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1785800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1320300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1282700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>429800</v>
+      </c>
+      <c r="E18" s="3">
         <v>386600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>405200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>325900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>323900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>285400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>302000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>365700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>213900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>210300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>202900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>192400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>180200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>201500</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E20" s="3">
         <v>41800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>103800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>30500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-80800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>27300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>19800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-15200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8300</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>534200</v>
+      </c>
+      <c r="E21" s="3">
         <v>455400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>425200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>405400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>461700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>499900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>415400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>504200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>210700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>201500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>187800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>181900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>246000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>268700</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E22" s="3">
         <v>68800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>65600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>59500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>68900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>52500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>58200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>77600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>51600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>56200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>71300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>34700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10900</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>370400</v>
+      </c>
+      <c r="E23" s="3">
         <v>297100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>274000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>238500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>250600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>314400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>220500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>277500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>159200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>145300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>116400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>147200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>162300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>198900</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E24" s="3">
         <v>98100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>122800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>54200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>77300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>81300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>80100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>84200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>55200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>46600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>26200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>29900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>49300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>52400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>236100</v>
+      </c>
+      <c r="E26" s="3">
         <v>199100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>151200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>184300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>173300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>233100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>140400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>193300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>104000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>98700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>90200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>117300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>113000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>146500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>234100</v>
+      </c>
+      <c r="E27" s="3">
         <v>195600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>147700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>181600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>171700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>231000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>139200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>191500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>102300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>98400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>89800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>115700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>112200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>146500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-41800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-103800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-30500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>80800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-27300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-19800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>234100</v>
+      </c>
+      <c r="E33" s="3">
         <v>195600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>147700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>181600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>171700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>231000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>139200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>191500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>102300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>98400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>89800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>115700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>112200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>146500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>234100</v>
+      </c>
+      <c r="E35" s="3">
         <v>195600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>147700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>181600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>171700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>231000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>139200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>191500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>102300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>98400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>89800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>115700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>112200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>146500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>327500</v>
+      </c>
+      <c r="E41" s="3">
         <v>346400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>343300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>357200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>435700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>209600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>198200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>221400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>45300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>94600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>104000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>32100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24900</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>75500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>109300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>228300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>197500</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>22200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>190800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>197300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>126800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>47400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>22400</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>344900</v>
+      </c>
+      <c r="E43" s="3">
         <v>409900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>394400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>337000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>290400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>281800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>268200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>306700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>213800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>204300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>244600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>269000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>202400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>228100</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>301900</v>
+      </c>
+      <c r="E44" s="3">
         <v>265800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>289400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>224600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>180100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>196400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>218100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>213400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>163500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>149300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>178200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>163600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>114300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>86800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E45" s="3">
         <v>9200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>223900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>49700</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1019600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1119800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1367500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1163100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1122200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>709500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>694000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>786400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>624600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>613100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>658900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>598800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>418800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>355700</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>85700</v>
+      </c>
+      <c r="E47" s="3">
         <v>121100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>131700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>125300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>139300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>148600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>161900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>161100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>94700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>70800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>147800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>109500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>102200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>101900</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1104700</v>
+      </c>
+      <c r="E48" s="3">
         <v>995100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>939600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>840800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>852300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>961200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1024300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1071900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>752800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>717400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>848600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>900800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>738000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>528600</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>145600</v>
+      </c>
+      <c r="E49" s="3">
         <v>933100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>942600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>912800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>989200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1059000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1132800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1229700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>885800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>852900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1005700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1061300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>677600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>88600</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>956300</v>
+      </c>
+      <c r="E52" s="3">
         <v>158200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>159400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>413500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>339600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>299300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>178200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>181400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>127100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>220300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>39300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>37400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>34500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>45600</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3311900</v>
+      </c>
+      <c r="E54" s="3">
         <v>3332400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3543900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3457900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3445600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3179800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3191300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3436100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2485000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2474500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2700300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2707800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1971000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1120400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>554900</v>
+      </c>
+      <c r="E57" s="3">
         <v>598200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>558500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>449700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>379800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>395400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>409200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>473500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>324300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>292500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>257900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>268300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>245700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>187700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>86700</v>
+      </c>
+      <c r="E58" s="3">
         <v>44400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>410300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>39400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>35500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>38600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>63000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>87200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>56600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>51400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>94000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>137600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>136000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>34900</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>270200</v>
+      </c>
+      <c r="E59" s="3">
         <v>81700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>91600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>91300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>73000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>62300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>85000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>76600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>93200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>82400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>136200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>116900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>60400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>74300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>911900</v>
+      </c>
+      <c r="E60" s="3">
         <v>790300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1117400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>621600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>532100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>547500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>605100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>695900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>474100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>426200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>488200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>522800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>442100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>296900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1010200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1131400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>933000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1221900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1320600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>988600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1032600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1098000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>815400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>857100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>864700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>785700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>222600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>112700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E62" s="3">
         <v>133300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>238100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>107400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>187000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>116300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>86000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>104100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>243900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>237400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>253900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>253500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>162500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>73500</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2291100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2281900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2504000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2165100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2275200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1891200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1946600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2114800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1557700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1544400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1632500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1589000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>852100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>483200</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>883700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>850300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>907900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>928400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>799200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>666100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>554000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>816800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>786100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>803200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>871400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>853700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>322400</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>982600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1010900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1006700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1263100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1141700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1261600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1216000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1285700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>927300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>930100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1067800</v>
-      </c>
-      <c r="N76" s="3">
-        <v>1118900</v>
       </c>
       <c r="O76" s="3">
         <v>1118900</v>
       </c>
       <c r="P76" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="Q76" s="3">
         <v>637200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>234100</v>
+      </c>
+      <c r="E81" s="3">
         <v>195600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>147700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>181600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>171700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>231000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>139200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>191500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>102300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>98400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>89800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>115700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>112200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>146500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,35 +3885,36 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>122900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>135300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>119700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>151000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>144500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>140500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>158100</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -3727,14 +3925,17 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>68900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>59700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>359500</v>
+      </c>
+      <c r="E89" s="3">
         <v>418400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>467800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>358000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>392400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>339300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>339100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>402900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>252500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>296700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>256500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>223700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>241700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>209800</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-219800</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
         <v>-219800</v>
       </c>
       <c r="F91" s="3">
+        <v>-219800</v>
+      </c>
+      <c r="G91" s="3">
         <v>-163000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-120900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-147200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-174500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-274400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-144900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-125900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-135900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-238800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-184000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-191700</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-291700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-180500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-232700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-315100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-146400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-170200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-274300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-128700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-115500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-198500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-581800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-199900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>189200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>322900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>124800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>140700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>114700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>126100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>121800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-76400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-60800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-62200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-95000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-89300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-107100</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-120500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-213400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-337800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-135400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>159100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-169100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-165200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-127300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-111000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-110400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-55800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>394000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-101400</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>5200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-25100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>11200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-19100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-15200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1300</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-52700</v>
+      </c>
+      <c r="E102" s="3">
         <v>29600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>217300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>29300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>55600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>31800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>AKO.B</t>
   </si>
@@ -988,8 +988,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>5600</v>
       </c>
       <c r="E14" s="3">
         <v>8300</v>
@@ -1037,13 +1037,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>122100</v>
+        <v>128000</v>
       </c>
       <c r="E15" s="3">
         <v>110500</v>
       </c>
       <c r="F15" s="3">
-        <v>123800</v>
+        <v>128700</v>
       </c>
       <c r="G15" s="3">
         <v>110000</v>
@@ -1102,7 +1102,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2814800</v>
+        <v>2845900</v>
       </c>
       <c r="E17" s="3">
         <v>2600000</v>
@@ -1150,7 +1150,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>429800</v>
+        <v>398700</v>
       </c>
       <c r="E18" s="3">
         <v>386600</v>
@@ -1218,7 +1218,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>17700</v>
+        <v>-21600</v>
       </c>
       <c r="E20" s="3">
         <v>41800</v>
@@ -1266,13 +1266,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>534200</v>
+        <v>548400</v>
       </c>
       <c r="E21" s="3">
         <v>455400</v>
       </c>
       <c r="F21" s="3">
-        <v>425200</v>
+        <v>430200</v>
       </c>
       <c r="G21" s="3">
         <v>405400</v>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>41700</v>
+        <v>62900</v>
       </c>
       <c r="E22" s="3">
         <v>68800</v>
@@ -1794,7 +1794,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-17700</v>
+        <v>21600</v>
       </c>
       <c r="E32" s="3">
         <v>-41800</v>
@@ -2079,7 +2079,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>327500</v>
+        <v>250500</v>
       </c>
       <c r="E41" s="3">
         <v>346400</v>
@@ -2127,7 +2127,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>72900</v>
       </c>
       <c r="E42" s="3">
         <v>75500</v>
@@ -2175,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>344900</v>
+        <v>362800</v>
       </c>
       <c r="E43" s="3">
         <v>409900</v>
@@ -2271,7 +2271,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>45300</v>
+        <v>15000</v>
       </c>
       <c r="E45" s="3">
         <v>9200</v>
@@ -2367,7 +2367,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>85700</v>
+        <v>110800</v>
       </c>
       <c r="E47" s="3">
         <v>121100</v>
@@ -2463,7 +2463,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>145600</v>
+        <v>843400</v>
       </c>
       <c r="E49" s="3">
         <v>933100</v>
@@ -2607,7 +2607,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>956300</v>
+        <v>225900</v>
       </c>
       <c r="E52" s="3">
         <v>158200</v>
@@ -2791,7 +2791,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>554900</v>
+        <v>554000</v>
       </c>
       <c r="E57" s="3">
         <v>598200</v>
@@ -2839,7 +2839,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>86700</v>
+        <v>96400</v>
       </c>
       <c r="E58" s="3">
         <v>44400</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>270200</v>
+        <v>188600</v>
       </c>
       <c r="E59" s="3">
         <v>81700</v>
@@ -2983,7 +2983,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1010200</v>
+        <v>1031200</v>
       </c>
       <c r="E61" s="3">
         <v>1131400</v>
@@ -3031,7 +3031,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>369000</v>
+        <v>101300</v>
       </c>
       <c r="E62" s="3">
         <v>133300</v>
@@ -3482,8 +3482,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>902900</v>
       </c>
       <c r="E72" s="3">
         <v>883700</v>
@@ -3891,14 +3891,14 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>144300</v>
       </c>
       <c r="E83" s="3">
         <v>122900</v>
       </c>
       <c r="F83" s="3">
-        <v>135300</v>
+        <v>140500</v>
       </c>
       <c r="G83" s="3">
         <v>119700</v>
@@ -4247,8 +4247,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-293400</v>
       </c>
       <c r="E91" s="3">
         <v>-219800</v>
@@ -4460,7 +4460,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>159400</v>
       </c>
       <c r="E96" s="3">
         <v>189200</v>
@@ -4699,8 +4699,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>13400</v>
       </c>
       <c r="E101" s="3">
         <v>5200</v>
@@ -4748,7 +4748,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-52700</v>
+        <v>-39300</v>
       </c>
       <c r="E102" s="3">
         <v>29600</v>

--- a/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AKO.B_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>AKO.B</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3713300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3244600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2986700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3127400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2601800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2390300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2366000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2410800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3004000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2008500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2102700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2138700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1978200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1500500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1484100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2262200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1957700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1827300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1917100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1614300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1439100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1394200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1395000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1736900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1168300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1239500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1286700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1189300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>894700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>873700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1451200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1287000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1159400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1210300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>987500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>951100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>971800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1015800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1267100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>840200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>863200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>852000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>788900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>605900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>610500</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,87 +998,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E14" s="3">
         <v>5600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8300</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-100</v>
       </c>
       <c r="G14" s="3">
         <v>-100</v>
       </c>
       <c r="H14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I14" s="3">
         <v>11200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3700</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>148700</v>
+      </c>
+      <c r="E15" s="3">
         <v>128000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>110500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>128700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>110000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>142100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>133700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>140700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>158300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3237000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2845900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2600000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2722200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2275900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2066300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2080600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2108800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2638300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1794600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1892400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1935700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1785800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1320300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1282700</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>476300</v>
+      </c>
+      <c r="E18" s="3">
         <v>398700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>386600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>405200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>325900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>323900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>285400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>302000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>365700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>213900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>210300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>202900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>192400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>180200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>201500</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-21600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>41800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>103800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>30500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-80800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>27300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>19800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-15200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8300</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>630000</v>
+      </c>
+      <c r="E21" s="3">
         <v>548400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>455400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>430200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>405400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>461700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>499900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>415400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>504200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>210700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>201500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>187800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>181900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>246000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>268700</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E22" s="3">
         <v>62900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>68800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>65600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>59500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>68900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>52500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>58200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>77600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>51600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>56200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>71300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>34700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10900</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>422600</v>
+      </c>
+      <c r="E23" s="3">
         <v>370400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>297100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>274000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>238500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>250600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>314400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>220500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>277500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>159200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>145300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>116400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>147200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>162300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>198900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E24" s="3">
         <v>134200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>98100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>122800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>54200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>77300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>81300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>80100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>84200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>55200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>26200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>29900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>49300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>52400</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300300</v>
+      </c>
+      <c r="E26" s="3">
         <v>236100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>199100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>151200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>184300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>173300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>233100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>140400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>193300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>104000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>98700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>90200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>117300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>113000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>146500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>298300</v>
+      </c>
+      <c r="E27" s="3">
         <v>234100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>195600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>147700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>181600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>171700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>231000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>139200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>191500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>102300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>98400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>89800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>115700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>112200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>146500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>21600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-41800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-103800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-30500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>80800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-27300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-19800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>15200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8300</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>298300</v>
+      </c>
+      <c r="E33" s="3">
         <v>234100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>195600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>147700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>181600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>171700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>231000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>139200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>191500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>102300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>98400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>89800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>115700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>112200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>146500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>298300</v>
+      </c>
+      <c r="E35" s="3">
         <v>234100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>195600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>147700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>181600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>171700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>231000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>139200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>191500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>102300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>98400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>89800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>115700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>112200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>146500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>329200</v>
+      </c>
+      <c r="E41" s="3">
         <v>250500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>346400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>343300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>357200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>435700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>209600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>198200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>221400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>45300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>94600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>104000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>32100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24900</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E42" s="3">
         <v>72900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>75500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>109300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>228300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>197500</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>22200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>190800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>197300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>126800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>47400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>22400</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>410900</v>
+      </c>
+      <c r="E43" s="3">
         <v>362800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>409900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>394400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>337000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>290400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>281800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>268200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>306700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>213800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>204300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>244600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>269000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>202400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>228100</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>338100</v>
+      </c>
+      <c r="E44" s="3">
         <v>301900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>265800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>289400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>224600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>180100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>196400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>218100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>213400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>163500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>149300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>178200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>163600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>114300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>86800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E45" s="3">
         <v>15000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>223900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>49700</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1146900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1019600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1119800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1367500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1163100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1122200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>709500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>694000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>786400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>624600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>613100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>658900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>598800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>418800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>355700</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E47" s="3">
         <v>110800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>121100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>131700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>125300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>139300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>148600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>161900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>161100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>94700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>70800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>147800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>109500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>102200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>101900</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1309300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1104700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>995100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>939600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>840800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>852300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>961200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1024300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1071900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>752800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>717400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>848600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>900800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>738000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>528600</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>951000</v>
+      </c>
+      <c r="E49" s="3">
         <v>843400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>933100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>942600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>912800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>989200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1059000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1132800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1229700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>885800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>852900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1005700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1061300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>677600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>88600</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>250800</v>
+      </c>
+      <c r="E52" s="3">
         <v>225900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>158200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>159400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>413500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>339600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>299300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>178200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>181400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>127100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>220300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>39300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>37400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>34500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>45600</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3797200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3311900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3332400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3543900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3457900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3445600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3179800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3191300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3436100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2485000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2474500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2700300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2707800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1971000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1120400</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>646100</v>
+      </c>
+      <c r="E57" s="3">
         <v>554000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>598200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>558500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>449700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>379800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>395400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>409200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>473500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>324300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>292500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>257900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>268300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>245700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>187700</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E58" s="3">
         <v>96400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>44400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>410300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>39400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>35500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>38600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>63000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>87200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>56600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>51400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>94000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>137600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>136000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>34900</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E59" s="3">
         <v>188600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>81700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>91600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>91300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>73000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>62300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>85000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>76600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>93200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>82400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>136200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>116900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>60400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>74300</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>810900</v>
+      </c>
+      <c r="E60" s="3">
         <v>911900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>790300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1117400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>621600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>532100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>547500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>605100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>695900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>474100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>426200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>488200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>522800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>442100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>296900</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1238000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1031200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1131400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>933000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1221900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1320600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>988600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1032600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1098000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>815400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>857100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>864700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>785700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>222600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>112700</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>151500</v>
+      </c>
+      <c r="E62" s="3">
         <v>101300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>133300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>238100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>107400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>187000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>116300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>86000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>104100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>243900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>237400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>253900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>253500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>162500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>73500</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2468800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2291100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2281900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2504000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2165100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2275200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1891200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1946600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2114800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1557700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1544400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1632500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1589000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>852100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>483200</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1304300</v>
+      </c>
+      <c r="E72" s="3">
         <v>902900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>883700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>850300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>907900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>928400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>799200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>666100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>554000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>816800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>786100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>803200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>871400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>853700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>322400</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1284900</v>
+      </c>
+      <c r="E76" s="3">
         <v>982600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1010900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1006700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1263100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1141700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1261600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1216000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1285700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>927300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>930100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1067800</v>
-      </c>
-      <c r="O76" s="3">
-        <v>1118900</v>
       </c>
       <c r="P76" s="3">
         <v>1118900</v>
       </c>
       <c r="Q76" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="R76" s="3">
         <v>637200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>298300</v>
+      </c>
+      <c r="E81" s="3">
         <v>234100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>195600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>147700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>181600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>171700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>231000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>139200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>191500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>102300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>98400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>89800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>115700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>112200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>146500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,38 +4083,39 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E83" s="3">
         <v>144300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>122900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>140500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>119700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>151000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>144500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>140500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>158100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -3928,14 +4126,17 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>68900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>59700</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>511900</v>
+      </c>
+      <c r="E89" s="3">
         <v>359500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>418400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>467800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>358000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>392400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>339300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>339100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>402900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>252500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>296700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>256500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>223700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>241700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>209800</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-308400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-293400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-219800</v>
       </c>
       <c r="F91" s="3">
         <v>-219800</v>
       </c>
       <c r="G91" s="3">
+        <v>-219800</v>
+      </c>
+      <c r="H91" s="3">
         <v>-163000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-120900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-147200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-174500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-274400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-144900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-125900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-135900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-238800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-184000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-191700</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-276000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-291700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-180500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-232700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-315100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-146400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-170200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-274300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-128700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-115500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-198500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-581800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-199900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-135300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E96" s="3">
         <v>159400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>189200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>322900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>124800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>140700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>114700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>126100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>121800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-76400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-60800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-62200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-95000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-89300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-107100</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-180300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-120500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-213400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-337800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-135400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>159100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-169100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-165200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-127300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-111000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-110400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-55800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>394000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-101400</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>13400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-25100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>11200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-19100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-15200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1300</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-39300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>217300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>29300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>55600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>31000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
